--- a/output/HydroAI_Forecast_All.xlsx
+++ b/output/HydroAI_Forecast_All.xlsx
@@ -10078,13 +10078,13 @@
         <v>9.51</v>
       </c>
       <c r="G254" t="n">
-        <v>378.6388663434112</v>
+        <v>377.995591343411</v>
       </c>
       <c r="H254" t="n">
-        <v>433.3725</v>
+        <v>432.7292249999998</v>
       </c>
       <c r="I254" t="n">
-        <v>463.0060044101025</v>
+        <v>462.3627294101023</v>
       </c>
       <c r="J254" t="n">
         <v>473.3365711667265</v>
@@ -10926,22 +10926,22 @@
         <v>6.85</v>
       </c>
       <c r="G276" t="n">
-        <v>182.2430429043371</v>
+        <v>183.1847095710038</v>
       </c>
       <c r="H276" t="n">
-        <v>209.6</v>
+        <v>210.5416666666667</v>
       </c>
       <c r="I276" t="n">
-        <v>241.5711378106951</v>
+        <v>242.5128044773618</v>
       </c>
       <c r="J276" t="n">
-        <v>483.4773361499354</v>
+        <v>483.621002816602</v>
       </c>
       <c r="K276" t="n">
-        <v>483.598</v>
+        <v>483.7416666666666</v>
       </c>
       <c r="L276" t="n">
-        <v>483.8201086780173</v>
+        <v>483.963775344684</v>
       </c>
     </row>
     <row r="277">
@@ -10955,7 +10955,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2019_2021_2020_operation_rule_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D277" t="n">
@@ -10970,22 +10970,22 @@
         <v>5.26</v>
       </c>
       <c r="G277" t="n">
-        <v>175.8658322105989</v>
+        <v>167.0597095710038</v>
       </c>
       <c r="H277" t="n">
-        <v>203.2227893062618</v>
+        <v>194.4166666666667</v>
       </c>
       <c r="I277" t="n">
-        <v>235.1939271169569</v>
+        <v>226.3878044773618</v>
       </c>
       <c r="J277" t="n">
-        <v>484.1454159890475</v>
+        <v>484.0747528166021</v>
       </c>
       <c r="K277" t="n">
-        <v>484.2660798391121</v>
+        <v>484.1954166666667</v>
       </c>
       <c r="L277" t="n">
-        <v>484.4881885171295</v>
+        <v>484.4175253446841</v>
       </c>
     </row>
     <row r="278">
@@ -10999,7 +10999,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2019_2021_2020_operation_rule_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D278" t="n">
@@ -11014,22 +11014,22 @@
         <v>7.8</v>
       </c>
       <c r="G278" t="n">
-        <v>146.7969888803828</v>
+        <v>142.3097095710038</v>
       </c>
       <c r="H278" t="n">
-        <v>174.1539459760456</v>
+        <v>169.6666666666667</v>
       </c>
       <c r="I278" t="n">
-        <v>206.1250837867408</v>
+        <v>201.6378044773618</v>
       </c>
       <c r="J278" t="n">
-        <v>484.1516941475301</v>
+        <v>484.5035028166021</v>
       </c>
       <c r="K278" t="n">
-        <v>484.2723579975947</v>
+        <v>484.6241666666667</v>
       </c>
       <c r="L278" t="n">
-        <v>484.494466675612</v>
+        <v>484.846275344684</v>
       </c>
     </row>
     <row r="279">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2019_2021_2020_operation_rule_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D279" t="n">
@@ -11058,22 +11058,22 @@
         <v>5.17</v>
       </c>
       <c r="G279" t="n">
-        <v>132.1692903892353</v>
+        <v>251.6865211652067</v>
       </c>
       <c r="H279" t="n">
-        <v>159.5262474848982</v>
+        <v>279.0434782608696</v>
       </c>
       <c r="I279" t="n">
-        <v>191.4973852955933</v>
+        <v>311.0146160715647</v>
       </c>
       <c r="J279" t="n">
-        <v>484.1455751892095</v>
+        <v>485.0106404977615</v>
       </c>
       <c r="K279" t="n">
-        <v>484.2662390392741</v>
+        <v>485.1313043478261</v>
       </c>
       <c r="L279" t="n">
-        <v>484.4883477172914</v>
+        <v>485.3534130258435</v>
       </c>
     </row>
     <row r="280">
@@ -11087,7 +11087,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2019_2021_2020_operation_rule_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D280" t="n">
@@ -11102,22 +11102,22 @@
         <v>5.51</v>
       </c>
       <c r="G280" t="n">
-        <v>105.9691301942456</v>
+        <v>183.4077487866901</v>
       </c>
       <c r="H280" t="n">
-        <v>133.3260872899085</v>
+        <v>210.7647058823529</v>
       </c>
       <c r="I280" t="n">
-        <v>165.2972251006036</v>
+        <v>242.7358436930481</v>
       </c>
       <c r="J280" t="n">
-        <v>484.1310675022322</v>
+        <v>485.3799243852295</v>
       </c>
       <c r="K280" t="n">
-        <v>484.2517313522968</v>
+        <v>485.5005882352941</v>
       </c>
       <c r="L280" t="n">
-        <v>484.4738400303142</v>
+        <v>485.7226969133115</v>
       </c>
     </row>
     <row r="281">
@@ -11131,7 +11131,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2019_2021_2020_operation_rule_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D281" t="n">
@@ -11146,22 +11146,22 @@
         <v>2.61</v>
       </c>
       <c r="G281" t="n">
-        <v>108.7767909921405</v>
+        <v>191.8097095710038</v>
       </c>
       <c r="H281" t="n">
-        <v>136.1337480878034</v>
+        <v>219.1666666666667</v>
       </c>
       <c r="I281" t="n">
-        <v>168.1048858984986</v>
+        <v>251.1378044773618</v>
       </c>
       <c r="J281" t="n">
-        <v>484.1036755834086</v>
+        <v>485.6439194832687</v>
       </c>
       <c r="K281" t="n">
-        <v>484.2243394334732</v>
+        <v>485.7645833333333</v>
       </c>
       <c r="L281" t="n">
-        <v>484.4464481114906</v>
+        <v>485.9866920113507</v>
       </c>
     </row>
     <row r="282">
@@ -11175,7 +11175,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2019_2021_2020_operation_rule_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D282" t="n">
@@ -11190,22 +11190,22 @@
         <v>6</v>
       </c>
       <c r="G282" t="n">
-        <v>108.9239228969284</v>
+        <v>188.1013762376705</v>
       </c>
       <c r="H282" t="n">
-        <v>136.2808799925913</v>
+        <v>215.4583333333333</v>
       </c>
       <c r="I282" t="n">
-        <v>168.2520178032864</v>
+        <v>247.4294711440285</v>
       </c>
       <c r="J282" t="n">
-        <v>484.0552236341934</v>
+        <v>485.934752816602</v>
       </c>
       <c r="K282" t="n">
-        <v>484.175887484258</v>
+        <v>486.0554166666666</v>
       </c>
       <c r="L282" t="n">
-        <v>484.3979961622754</v>
+        <v>486.277525344684</v>
       </c>
     </row>
     <row r="283">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2019_2021_2020_operation_rule_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D283" t="n">
@@ -11234,22 +11234,22 @@
         <v>3.95</v>
       </c>
       <c r="G283" t="n">
-        <v>118.3713829987016</v>
+        <v>175.9347095710038</v>
       </c>
       <c r="H283" t="n">
-        <v>145.7283400943645</v>
+        <v>203.2916666666667</v>
       </c>
       <c r="I283" t="n">
-        <v>177.6994779050596</v>
+        <v>235.2628044773618</v>
       </c>
       <c r="J283" t="n">
-        <v>483.9956214419917</v>
+        <v>486.1418361499354</v>
       </c>
       <c r="K283" t="n">
-        <v>484.1162852920563</v>
+        <v>486.2625</v>
       </c>
       <c r="L283" t="n">
-        <v>484.3383939700737</v>
+        <v>486.4846086780174</v>
       </c>
     </row>
     <row r="284">
@@ -11263,7 +11263,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2019_2021_2020_operation_rule_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D284" t="n">
@@ -11278,22 +11278,22 @@
         <v>3.57</v>
       </c>
       <c r="G284" t="n">
-        <v>115.9748843433779</v>
+        <v>190.3513762376705</v>
       </c>
       <c r="H284" t="n">
-        <v>143.3318414390407</v>
+        <v>217.7083333333333</v>
       </c>
       <c r="I284" t="n">
-        <v>175.3029792497359</v>
+        <v>249.6794711440285</v>
       </c>
       <c r="J284" t="n">
-        <v>483.9318515914073</v>
+        <v>486.2630861499354</v>
       </c>
       <c r="K284" t="n">
-        <v>484.0525154414719</v>
+        <v>486.38375</v>
       </c>
       <c r="L284" t="n">
-        <v>484.2746241194893</v>
+        <v>486.6058586780173</v>
       </c>
     </row>
     <row r="285">
@@ -11307,7 +11307,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2019_2021_2020_operation_rule_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D285" t="n">
@@ -11322,22 +11322,22 @@
         <v>3.99</v>
       </c>
       <c r="G285" t="n">
-        <v>132.2996897528523</v>
+        <v>176.7680429043371</v>
       </c>
       <c r="H285" t="n">
-        <v>159.6566468485152</v>
+        <v>204.125</v>
       </c>
       <c r="I285" t="n">
-        <v>191.6277846592104</v>
+        <v>236.0961378106952</v>
       </c>
       <c r="J285" t="n">
-        <v>483.871639684819</v>
+        <v>486.3568361499354</v>
       </c>
       <c r="K285" t="n">
-        <v>483.9923035348836</v>
+        <v>486.4775</v>
       </c>
       <c r="L285" t="n">
-        <v>484.214412212901</v>
+        <v>486.6996086780174</v>
       </c>
     </row>
     <row r="286">
@@ -11351,7 +11351,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2019_2021_2020_operation_rule_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D286" t="n">
@@ -11366,22 +11366,22 @@
         <v>2.53</v>
       </c>
       <c r="G286" t="n">
-        <v>121.1108064520848</v>
+        <v>148.3097095710038</v>
       </c>
       <c r="H286" t="n">
-        <v>148.4677635477476</v>
+        <v>175.6666666666667</v>
       </c>
       <c r="I286" t="n">
-        <v>180.4389013584428</v>
+        <v>207.6378044773618</v>
       </c>
       <c r="J286" t="n">
-        <v>483.8058534268346</v>
+        <v>486.3351694832688</v>
       </c>
       <c r="K286" t="n">
-        <v>483.9265172768992</v>
+        <v>486.4558333333334</v>
       </c>
       <c r="L286" t="n">
-        <v>484.1486259549166</v>
+        <v>486.6779420113508</v>
       </c>
     </row>
     <row r="287">
@@ -11395,7 +11395,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2019_2021_2020_operation_rule_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D287" t="n">
@@ -11410,22 +11410,22 @@
         <v>6.37</v>
       </c>
       <c r="G287" t="n">
-        <v>121.8016627883158</v>
+        <v>163.5597095710038</v>
       </c>
       <c r="H287" t="n">
-        <v>149.1586198839786</v>
+        <v>190.9166666666667</v>
       </c>
       <c r="I287" t="n">
-        <v>181.1297576946738</v>
+        <v>222.8878044773618</v>
       </c>
       <c r="J287" t="n">
-        <v>483.7713037915772</v>
+        <v>486.308502816602</v>
       </c>
       <c r="K287" t="n">
-        <v>483.8919676416418</v>
+        <v>486.4291666666666</v>
       </c>
       <c r="L287" t="n">
-        <v>484.1140763196592</v>
+        <v>486.651275344684</v>
       </c>
     </row>
     <row r="288">
@@ -11439,7 +11439,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2019_2021_2020_operation_rule_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D288" t="n">
@@ -11454,22 +11454,22 @@
         <v>6.26</v>
       </c>
       <c r="G288" t="n">
-        <v>126.3214383934498</v>
+        <v>175.4763762376705</v>
       </c>
       <c r="H288" t="n">
-        <v>153.6783954891126</v>
+        <v>202.8333333333333</v>
       </c>
       <c r="I288" t="n">
-        <v>185.6495332998078</v>
+        <v>234.8044711440285</v>
       </c>
       <c r="J288" t="n">
-        <v>483.761734441211</v>
+        <v>486.3618361499354</v>
       </c>
       <c r="K288" t="n">
-        <v>483.8823982912756</v>
+        <v>486.4825</v>
       </c>
       <c r="L288" t="n">
-        <v>484.104506969293</v>
+        <v>486.7046086780174</v>
       </c>
     </row>
     <row r="289">
@@ -11483,7 +11483,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2019_2021_2020_operation_rule_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D289" t="n">
@@ -11498,22 +11498,22 @@
         <v>4.44</v>
       </c>
       <c r="G289" t="n">
-        <v>126.5350530603437</v>
+        <v>155.0343472521632</v>
       </c>
       <c r="H289" t="n">
-        <v>153.8920101560065</v>
+        <v>182.3913043478261</v>
       </c>
       <c r="I289" t="n">
-        <v>185.8631479667017</v>
+        <v>214.3624421585212</v>
       </c>
       <c r="J289" t="n">
-        <v>483.7633353776662</v>
+        <v>486.3575970195006</v>
       </c>
       <c r="K289" t="n">
-        <v>483.8839992277308</v>
+        <v>486.4782608695652</v>
       </c>
       <c r="L289" t="n">
-        <v>484.1061079057482</v>
+        <v>486.7003695475826</v>
       </c>
     </row>
     <row r="290">
@@ -11527,7 +11527,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2019_2021_2020_operation_rule_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D290" t="n">
@@ -11542,22 +11542,22 @@
         <v>5.48</v>
       </c>
       <c r="G290" t="n">
-        <v>145.5795665197776</v>
+        <v>127.5377797464424</v>
       </c>
       <c r="H290" t="n">
-        <v>172.9365236154404</v>
+        <v>154.8947368421053</v>
       </c>
       <c r="I290" t="n">
-        <v>204.9076614261356</v>
+        <v>186.8658746528004</v>
       </c>
       <c r="J290" t="n">
-        <v>483.7752254138609</v>
+        <v>486.3019677288828</v>
       </c>
       <c r="K290" t="n">
-        <v>483.8958892639255</v>
+        <v>486.4226315789474</v>
       </c>
       <c r="L290" t="n">
-        <v>484.1179979419429</v>
+        <v>486.6447402569648</v>
       </c>
     </row>
     <row r="291">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2019_2021_2020_operation_rule_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D291" t="n">
@@ -11586,22 +11586,22 @@
         <v>2.44</v>
       </c>
       <c r="G291" t="n">
-        <v>144.475493097008</v>
+        <v>133.1013762376705</v>
       </c>
       <c r="H291" t="n">
-        <v>171.8324501926709</v>
+        <v>160.4583333333333</v>
       </c>
       <c r="I291" t="n">
-        <v>203.803588003366</v>
+        <v>192.4294711440285</v>
       </c>
       <c r="J291" t="n">
-        <v>483.8306437193473</v>
+        <v>486.2530861499354</v>
       </c>
       <c r="K291" t="n">
-        <v>483.9513075694119</v>
+        <v>486.37375</v>
       </c>
       <c r="L291" t="n">
-        <v>484.1734162474293</v>
+        <v>486.5958586780174</v>
       </c>
     </row>
     <row r="292">
@@ -11615,7 +11615,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2019_2021_2020_operation_rule_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D292" t="n">
@@ -11630,22 +11630,22 @@
         <v>1.66</v>
       </c>
       <c r="G292" t="n">
-        <v>143.62589800285</v>
+        <v>128.7680429043371</v>
       </c>
       <c r="H292" t="n">
-        <v>170.9828550985129</v>
+        <v>156.125</v>
       </c>
       <c r="I292" t="n">
-        <v>202.953992909208</v>
+        <v>188.0961378106952</v>
       </c>
       <c r="J292" t="n">
-        <v>483.9130948016622</v>
+        <v>486.2230861499354</v>
       </c>
       <c r="K292" t="n">
-        <v>484.0337586517268</v>
+        <v>486.34375</v>
       </c>
       <c r="L292" t="n">
-        <v>484.2558673297441</v>
+        <v>486.5658586780174</v>
       </c>
     </row>
     <row r="293">
@@ -11659,7 +11659,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2019_2021_2020_operation_rule_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D293" t="n">
@@ -11674,22 +11674,22 @@
         <v>1.47</v>
       </c>
       <c r="G293" t="n">
-        <v>134.2281210314382</v>
+        <v>164.6013762376705</v>
       </c>
       <c r="H293" t="n">
-        <v>161.585078127101</v>
+        <v>191.9583333333333</v>
       </c>
       <c r="I293" t="n">
-        <v>193.5562159377962</v>
+        <v>223.9294711440285</v>
       </c>
       <c r="J293" t="n">
-        <v>484.0079069723852</v>
+        <v>486.2243361499354</v>
       </c>
       <c r="K293" t="n">
-        <v>484.1285708224498</v>
+        <v>486.345</v>
       </c>
       <c r="L293" t="n">
-        <v>484.3506795004672</v>
+        <v>486.5671086780174</v>
       </c>
     </row>
     <row r="294">
@@ -11703,7 +11703,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2019_2021_2020_operation_rule_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D294" t="n">
@@ -11718,22 +11718,22 @@
         <v>1.26</v>
       </c>
       <c r="G294" t="n">
-        <v>130.7826931862242</v>
+        <v>153.8513762376705</v>
       </c>
       <c r="H294" t="n">
-        <v>158.139650281887</v>
+        <v>181.2083333333333</v>
       </c>
       <c r="I294" t="n">
-        <v>190.1107880925822</v>
+        <v>213.1794711440285</v>
       </c>
       <c r="J294" t="n">
-        <v>484.116760502146</v>
+        <v>486.2547528166021</v>
       </c>
       <c r="K294" t="n">
-        <v>484.2374243522106</v>
+        <v>486.3754166666667</v>
       </c>
       <c r="L294" t="n">
-        <v>484.459533030228</v>
+        <v>486.5975253446841</v>
       </c>
     </row>
     <row r="295">
@@ -11747,7 +11747,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2019_2021_2020_operation_rule_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D295" t="n">
@@ -11762,22 +11762,22 @@
         <v>2.3</v>
       </c>
       <c r="G295" t="n">
-        <v>133.9439335937882</v>
+        <v>171.3097095710038</v>
       </c>
       <c r="H295" t="n">
-        <v>161.3008906894511</v>
+        <v>198.6666666666667</v>
       </c>
       <c r="I295" t="n">
-        <v>193.2720285001462</v>
+        <v>230.6378044773618</v>
       </c>
       <c r="J295" t="n">
-        <v>484.23212383087</v>
+        <v>486.2946694832687</v>
       </c>
       <c r="K295" t="n">
-        <v>484.3527876809346</v>
+        <v>486.4153333333333</v>
       </c>
       <c r="L295" t="n">
-        <v>484.574896358952</v>
+        <v>486.6374420113507</v>
       </c>
     </row>
     <row r="296">
@@ -11806,22 +11806,22 @@
         <v>4.07</v>
       </c>
       <c r="G296" t="n">
-        <v>122.2945683332044</v>
+        <v>192.3961312410999</v>
       </c>
       <c r="H296" t="n">
-        <v>149.6515254288673</v>
+        <v>219.7530883367627</v>
       </c>
       <c r="I296" t="n">
-        <v>181.6226632395625</v>
+        <v>251.7242261474579</v>
       </c>
       <c r="J296" t="n">
-        <v>484.3347198599411</v>
+        <v>486.5922785273254</v>
       </c>
       <c r="K296" t="n">
-        <v>484.4553837100057</v>
+        <v>486.71294237739</v>
       </c>
       <c r="L296" t="n">
-        <v>484.677492388023</v>
+        <v>486.9350510554074</v>
       </c>
     </row>
     <row r="297">
@@ -11850,22 +11850,22 @@
         <v>1.73</v>
       </c>
       <c r="G297" t="n">
-        <v>125.266582440068</v>
+        <v>174.4045388804262</v>
       </c>
       <c r="H297" t="n">
-        <v>152.6235395357308</v>
+        <v>201.7614959760891</v>
       </c>
       <c r="I297" t="n">
-        <v>184.594677346426</v>
+        <v>233.7326337867842</v>
       </c>
       <c r="J297" t="n">
-        <v>484.4170167561383</v>
+        <v>486.6789538261013</v>
       </c>
       <c r="K297" t="n">
-        <v>484.5376806062029</v>
+        <v>486.799617676166</v>
       </c>
       <c r="L297" t="n">
-        <v>484.7597892842203</v>
+        <v>487.0217263541833</v>
       </c>
     </row>
     <row r="298">
@@ -11894,22 +11894,22 @@
         <v>0.78</v>
       </c>
       <c r="G298" t="n">
-        <v>114.8754401915965</v>
+        <v>140.2590359107626</v>
       </c>
       <c r="H298" t="n">
-        <v>142.2323972872593</v>
+        <v>167.6159930064255</v>
       </c>
       <c r="I298" t="n">
-        <v>174.2035350979545</v>
+        <v>199.5871308171206</v>
       </c>
       <c r="J298" t="n">
-        <v>484.4911138416238</v>
+        <v>486.750368956218</v>
       </c>
       <c r="K298" t="n">
-        <v>484.6117776916884</v>
+        <v>486.8710328062826</v>
       </c>
       <c r="L298" t="n">
-        <v>484.8338863697058</v>
+        <v>487.0931414843</v>
       </c>
     </row>
     <row r="299">
@@ -11938,22 +11938,22 @@
         <v>2.11</v>
       </c>
       <c r="G299" t="n">
-        <v>114.4217222565504</v>
+        <v>119.8040712316974</v>
       </c>
       <c r="H299" t="n">
-        <v>141.7786793522132</v>
+        <v>147.1610283273603</v>
       </c>
       <c r="I299" t="n">
-        <v>173.7498171629084</v>
+        <v>179.1321661380555</v>
       </c>
       <c r="J299" t="n">
-        <v>484.5510670395029</v>
+        <v>486.8114942291029</v>
       </c>
       <c r="K299" t="n">
-        <v>484.6717308895675</v>
+        <v>486.9321580791675</v>
       </c>
       <c r="L299" t="n">
-        <v>484.8938395675848</v>
+        <v>487.1542667571849</v>
       </c>
     </row>
     <row r="300">
@@ -11982,22 +11982,22 @@
         <v>1.2</v>
       </c>
       <c r="G300" t="n">
-        <v>109.1981362727108</v>
+        <v>112.7124525063227</v>
       </c>
       <c r="H300" t="n">
-        <v>136.5550933683737</v>
+        <v>140.0694096019856</v>
       </c>
       <c r="I300" t="n">
-        <v>168.5262311790688</v>
+        <v>172.0405474126807</v>
       </c>
       <c r="J300" t="n">
-        <v>484.6019469115685</v>
+        <v>486.8633687941697</v>
       </c>
       <c r="K300" t="n">
-        <v>484.7226107616331</v>
+        <v>486.9840326442343</v>
       </c>
       <c r="L300" t="n">
-        <v>484.9447194396505</v>
+        <v>487.2061413222517</v>
       </c>
     </row>
     <row r="301">
@@ -12026,22 +12026,22 @@
         <v>1.72</v>
       </c>
       <c r="G301" t="n">
-        <v>118.1497697068779</v>
+        <v>120.1152750719571</v>
       </c>
       <c r="H301" t="n">
-        <v>145.5067268025407</v>
+        <v>147.4722321676199</v>
       </c>
       <c r="I301" t="n">
-        <v>177.4778646132359</v>
+        <v>179.4433699783151</v>
       </c>
       <c r="J301" t="n">
-        <v>484.6460393956881</v>
+        <v>486.9083232789901</v>
       </c>
       <c r="K301" t="n">
-        <v>484.7667032457528</v>
+        <v>487.0289871290547</v>
       </c>
       <c r="L301" t="n">
-        <v>484.9888119237701</v>
+        <v>487.251095807072</v>
       </c>
     </row>
     <row r="302">
@@ -12070,22 +12070,22 @@
         <v>0.3</v>
       </c>
       <c r="G302" t="n">
-        <v>126.818716627784</v>
+        <v>127.01613666899</v>
       </c>
       <c r="H302" t="n">
-        <v>154.1756737234469</v>
+        <v>154.3730937646529</v>
       </c>
       <c r="I302" t="n">
-        <v>186.146811534142</v>
+        <v>186.344231575348</v>
       </c>
       <c r="J302" t="n">
-        <v>484.6811682403106</v>
+        <v>486.944138886658</v>
       </c>
       <c r="K302" t="n">
-        <v>484.8018320903752</v>
+        <v>487.0648027367226</v>
       </c>
       <c r="L302" t="n">
-        <v>485.0239407683926</v>
+        <v>487.28691141474</v>
       </c>
     </row>
     <row r="303">
@@ -12114,22 +12114,22 @@
         <v>1.77</v>
       </c>
       <c r="G303" t="n">
-        <v>114.0390465481125</v>
+        <v>112.3407284173484</v>
       </c>
       <c r="H303" t="n">
-        <v>141.3960036437753</v>
+        <v>139.6976855130112</v>
       </c>
       <c r="I303" t="n">
-        <v>173.3671414544705</v>
+        <v>171.6688233237064</v>
       </c>
       <c r="J303" t="n">
-        <v>484.7245729761896</v>
+        <v>486.9883708803283</v>
       </c>
       <c r="K303" t="n">
-        <v>484.8452368262542</v>
+        <v>487.1090347303929</v>
       </c>
       <c r="L303" t="n">
-        <v>485.0673455042716</v>
+        <v>487.3311434084103</v>
       </c>
     </row>
     <row r="304">
@@ -12158,22 +12158,22 @@
         <v>2.26</v>
       </c>
       <c r="G304" t="n">
-        <v>110.7086615655359</v>
+        <v>108.8995823407067</v>
       </c>
       <c r="H304" t="n">
-        <v>138.0656186611987</v>
+        <v>136.2565394363696</v>
       </c>
       <c r="I304" t="n">
-        <v>170.0367564718939</v>
+        <v>168.2276772470647</v>
       </c>
       <c r="J304" t="n">
-        <v>484.7670023154726</v>
+        <v>487.0315879241533</v>
       </c>
       <c r="K304" t="n">
-        <v>484.8876661655372</v>
+        <v>487.1522517742179</v>
       </c>
       <c r="L304" t="n">
-        <v>485.1097748435546</v>
+        <v>487.3743604522353</v>
       </c>
     </row>
     <row r="305">
@@ -12202,22 +12202,22 @@
         <v>4.21</v>
       </c>
       <c r="G305" t="n">
-        <v>120.2446498207167</v>
+        <v>118.1451599095817</v>
       </c>
       <c r="H305" t="n">
-        <v>147.6016069163795</v>
+        <v>145.5021170052445</v>
       </c>
       <c r="I305" t="n">
-        <v>179.5727447270747</v>
+        <v>177.4732548159397</v>
       </c>
       <c r="J305" t="n">
-        <v>484.8059823117486</v>
+        <v>487.0712721950765</v>
       </c>
       <c r="K305" t="n">
-        <v>484.9266461618132</v>
+        <v>487.1919360451411</v>
       </c>
       <c r="L305" t="n">
-        <v>485.1487548398305</v>
+        <v>487.4140447231585</v>
       </c>
     </row>
     <row r="306">
@@ -12246,22 +12246,22 @@
         <v>0.66</v>
       </c>
       <c r="G306" t="n">
-        <v>48.97951093370705</v>
+        <v>46.76678756521193</v>
       </c>
       <c r="H306" t="n">
-        <v>143.9148535034189</v>
+        <v>141.7021301349237</v>
       </c>
       <c r="I306" t="n">
-        <v>176.9450980363518</v>
+        <v>174.7323746678567</v>
       </c>
       <c r="J306" t="n">
-        <v>484.8424570701524</v>
+        <v>487.1085282417956</v>
       </c>
       <c r="K306" t="n">
-        <v>484.9711218821607</v>
+        <v>487.2371930538038</v>
       </c>
       <c r="L306" t="n">
-        <v>485.1348522727362</v>
+        <v>487.4009234443793</v>
       </c>
     </row>
     <row r="307">
@@ -12290,22 +12290,22 @@
         <v>0.15</v>
       </c>
       <c r="G307" t="n">
-        <v>33.63444510906507</v>
+        <v>31.50560465301777</v>
       </c>
       <c r="H307" t="n">
-        <v>128.5697876787769</v>
+        <v>126.4409472227296</v>
       </c>
       <c r="I307" t="n">
-        <v>161.6000322117098</v>
+        <v>159.4711917556625</v>
       </c>
       <c r="J307" t="n">
-        <v>484.8901127857508</v>
+        <v>487.1569970666578</v>
       </c>
       <c r="K307" t="n">
-        <v>485.018777597759</v>
+        <v>487.285661878666</v>
       </c>
       <c r="L307" t="n">
-        <v>485.1825079883345</v>
+        <v>487.4493922692415</v>
       </c>
     </row>
     <row r="308">
@@ -12334,22 +12334,22 @@
         <v>3.36</v>
       </c>
       <c r="G308" t="n">
-        <v>94.89967267320802</v>
+        <v>91.52568980213042</v>
       </c>
       <c r="H308" t="n">
-        <v>189.8350152429198</v>
+        <v>186.4610323718422</v>
       </c>
       <c r="I308" t="n">
-        <v>222.8652597758528</v>
+        <v>219.4912769047752</v>
       </c>
       <c r="J308" t="n">
-        <v>484.913187074311</v>
+        <v>487.1804533303886</v>
       </c>
       <c r="K308" t="n">
-        <v>485.0418518863193</v>
+        <v>487.3091181423969</v>
       </c>
       <c r="L308" t="n">
-        <v>485.2055822768947</v>
+        <v>487.4728485329724</v>
       </c>
     </row>
     <row r="309">
@@ -12378,22 +12378,22 @@
         <v>1.4</v>
       </c>
       <c r="G309" t="n">
-        <v>103.3623697655582</v>
+        <v>112.1298629680354</v>
       </c>
       <c r="H309" t="n">
-        <v>198.29771233527</v>
+        <v>207.0652055377472</v>
       </c>
       <c r="I309" t="n">
-        <v>231.327956868203</v>
+        <v>240.0954500706802</v>
       </c>
       <c r="J309" t="n">
-        <v>484.9439793027711</v>
+        <v>487.211739545053</v>
       </c>
       <c r="K309" t="n">
-        <v>485.0726441147793</v>
+        <v>487.3404043570612</v>
       </c>
       <c r="L309" t="n">
-        <v>485.2363745053548</v>
+        <v>487.5</v>
       </c>
     </row>
     <row r="310">
@@ -12422,22 +12422,22 @@
         <v>0</v>
       </c>
       <c r="G310" t="n">
-        <v>93.32965013347831</v>
+        <v>89.74833405645393</v>
       </c>
       <c r="H310" t="n">
-        <v>188.2649927031901</v>
+        <v>184.6836766261657</v>
       </c>
       <c r="I310" t="n">
-        <v>221.2952372361231</v>
+        <v>217.7139211590987</v>
       </c>
       <c r="J310" t="n">
-        <v>484.9880874115282</v>
+        <v>487.256555260837</v>
       </c>
       <c r="K310" t="n">
-        <v>485.1167522235365</v>
+        <v>487.3852200728452</v>
       </c>
       <c r="L310" t="n">
-        <v>485.280482614112</v>
+        <v>487.5</v>
       </c>
     </row>
     <row r="311">
@@ -12466,22 +12466,22 @@
         <v>1.24</v>
       </c>
       <c r="G311" t="n">
-        <v>103.3623697655582</v>
+        <v>110.2867978034186</v>
       </c>
       <c r="H311" t="n">
-        <v>198.29771233527</v>
+        <v>205.2221403731304</v>
       </c>
       <c r="I311" t="n">
-        <v>231.327956868203</v>
+        <v>238.2523849060634</v>
       </c>
       <c r="J311" t="n">
-        <v>485.0199767392269</v>
+        <v>487.2889561750216</v>
       </c>
       <c r="K311" t="n">
-        <v>485.1486415512352</v>
+        <v>487.4176209870299</v>
       </c>
       <c r="L311" t="n">
-        <v>485.3123719418107</v>
+        <v>487.5</v>
       </c>
     </row>
     <row r="312">
@@ -12510,22 +12510,22 @@
         <v>0.79</v>
       </c>
       <c r="G312" t="n">
-        <v>103.3623697655582</v>
+        <v>115.7333937925515</v>
       </c>
       <c r="H312" t="n">
-        <v>198.29771233527</v>
+        <v>210.6687363622634</v>
       </c>
       <c r="I312" t="n">
-        <v>231.327956868203</v>
+        <v>243.6989808951963</v>
       </c>
       <c r="J312" t="n">
-        <v>485.0421107199</v>
+        <v>487.3114452414306</v>
       </c>
       <c r="K312" t="n">
-        <v>485.1707755319082</v>
+        <v>487.4401100534388</v>
       </c>
       <c r="L312" t="n">
-        <v>485.3345059224837</v>
+        <v>487.5</v>
       </c>
     </row>
     <row r="313">
@@ -12554,22 +12554,22 @@
         <v>0.58</v>
       </c>
       <c r="G313" t="n">
-        <v>103.3623697655582</v>
+        <v>115.7333937925515</v>
       </c>
       <c r="H313" t="n">
-        <v>198.29771233527</v>
+        <v>210.6687363622634</v>
       </c>
       <c r="I313" t="n">
-        <v>231.327956868203</v>
+        <v>243.6989808951963</v>
       </c>
       <c r="J313" t="n">
-        <v>485.0709080621754</v>
+        <v>487.340704566827</v>
       </c>
       <c r="K313" t="n">
-        <v>485.1995728741836</v>
+        <v>487.4693693788353</v>
       </c>
       <c r="L313" t="n">
-        <v>485.3633032647591</v>
+        <v>487.5</v>
       </c>
     </row>
     <row r="314">
@@ -12598,22 +12598,22 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="G314" t="n">
-        <v>103.3623697655582</v>
+        <v>100.9719407474421</v>
       </c>
       <c r="H314" t="n">
-        <v>198.29771233527</v>
+        <v>195.9072833171539</v>
       </c>
       <c r="I314" t="n">
-        <v>231.327956868203</v>
+        <v>228.9375278500869</v>
       </c>
       <c r="J314" t="n">
-        <v>485.1044820166715</v>
+        <v>487.3713351879917</v>
       </c>
       <c r="K314" t="n">
-        <v>485.2331468286797</v>
+        <v>487.5</v>
       </c>
       <c r="L314" t="n">
-        <v>485.3968772192552</v>
+        <v>487.5</v>
       </c>
     </row>
     <row r="315">
@@ -12642,22 +12642,22 @@
         <v>0.44</v>
       </c>
       <c r="G315" t="n">
-        <v>103.3623697655582</v>
+        <v>112.7432279253877</v>
       </c>
       <c r="H315" t="n">
-        <v>198.29771233527</v>
+        <v>207.6785704950995</v>
       </c>
       <c r="I315" t="n">
-        <v>231.327956868203</v>
+        <v>240.7088150280325</v>
       </c>
       <c r="J315" t="n">
-        <v>485.1222108735352</v>
+        <v>487.3713351879917</v>
       </c>
       <c r="K315" t="n">
-        <v>485.2508756855434</v>
+        <v>487.5</v>
       </c>
       <c r="L315" t="n">
-        <v>485.4146060761189</v>
+        <v>487.5</v>
       </c>
     </row>
     <row r="316">
@@ -12686,22 +12686,22 @@
         <v>2.36</v>
       </c>
       <c r="G316" t="n">
-        <v>103.3623697655582</v>
+        <v>115.7333937925515</v>
       </c>
       <c r="H316" t="n">
-        <v>198.29771233527</v>
+        <v>210.6687363622634</v>
       </c>
       <c r="I316" t="n">
-        <v>231.327956868203</v>
+        <v>243.6989808951963</v>
       </c>
       <c r="J316" t="n">
-        <v>485.1355992721987</v>
+        <v>487.3713351879917</v>
       </c>
       <c r="K316" t="n">
-        <v>485.264264084207</v>
+        <v>487.5</v>
       </c>
       <c r="L316" t="n">
-        <v>485.4279944747825</v>
+        <v>487.5</v>
       </c>
     </row>
     <row r="317">
@@ -12730,22 +12730,22 @@
         <v>0.15</v>
       </c>
       <c r="G317" t="n">
-        <v>103.3623697655582</v>
+        <v>100.3526867998113</v>
       </c>
       <c r="H317" t="n">
-        <v>198.29771233527</v>
+        <v>195.2880293695231</v>
       </c>
       <c r="I317" t="n">
-        <v>231.327956868203</v>
+        <v>228.318273902456</v>
       </c>
       <c r="J317" t="n">
-        <v>485.1462928197671</v>
+        <v>487.3713351879917</v>
       </c>
       <c r="K317" t="n">
-        <v>485.2749576317754</v>
+        <v>487.5</v>
       </c>
       <c r="L317" t="n">
-        <v>485.4386880223508</v>
+        <v>487.5</v>
       </c>
     </row>
     <row r="318">
@@ -12774,22 +12774,22 @@
         <v>0.04</v>
       </c>
       <c r="G318" t="n">
-        <v>76.77457636818968</v>
+        <v>73.50818316121487</v>
       </c>
       <c r="H318" t="n">
-        <v>171.7099189379015</v>
+        <v>168.4435257309267</v>
       </c>
       <c r="I318" t="n">
-        <v>204.7401634708345</v>
+        <v>201.4737702638596</v>
       </c>
       <c r="J318" t="n">
-        <v>485.1546245887703</v>
+        <v>487.3713351879917</v>
       </c>
       <c r="K318" t="n">
-        <v>485.2832894007786</v>
+        <v>487.5</v>
       </c>
       <c r="L318" t="n">
-        <v>485.4470197913541</v>
+        <v>487.5</v>
       </c>
     </row>
     <row r="319">
@@ -12818,22 +12818,22 @@
         <v>0.13</v>
       </c>
       <c r="G319" t="n">
-        <v>65.682164018067</v>
+        <v>62.62677889130978</v>
       </c>
       <c r="H319" t="n">
-        <v>160.6175065877788</v>
+        <v>157.5621214610216</v>
       </c>
       <c r="I319" t="n">
-        <v>193.6477511207118</v>
+        <v>190.5923659939546</v>
       </c>
       <c r="J319" t="n">
-        <v>485.1541821353797</v>
+        <v>487.3713351879917</v>
       </c>
       <c r="K319" t="n">
-        <v>485.282846947388</v>
+        <v>487.5</v>
       </c>
       <c r="L319" t="n">
-        <v>485.4465773379634</v>
+        <v>487.5</v>
       </c>
     </row>
     <row r="320">
@@ -12862,22 +12862,22 @@
         <v>0.78</v>
       </c>
       <c r="G320" t="n">
-        <v>60.19840475763348</v>
+        <v>57.24733575954116</v>
       </c>
       <c r="H320" t="n">
-        <v>155.1337473273453</v>
+        <v>152.182678329253</v>
       </c>
       <c r="I320" t="n">
-        <v>188.1639918602783</v>
+        <v>185.2129228621859</v>
       </c>
       <c r="J320" t="n">
-        <v>485.143945147586</v>
+        <v>487.3713351879917</v>
       </c>
       <c r="K320" t="n">
-        <v>485.2726099595943</v>
+        <v>487.5</v>
       </c>
       <c r="L320" t="n">
-        <v>485.4363403501698</v>
+        <v>487.5</v>
       </c>
     </row>
     <row r="321">
@@ -12906,22 +12906,22 @@
         <v>0.83</v>
       </c>
       <c r="G321" t="n">
-        <v>42.14819556608958</v>
+        <v>39.54049101107904</v>
       </c>
       <c r="H321" t="n">
-        <v>137.0835381358014</v>
+        <v>134.4758335807909</v>
       </c>
       <c r="I321" t="n">
-        <v>170.1137826687344</v>
+        <v>167.5060781137238</v>
       </c>
       <c r="J321" t="n">
-        <v>485.1381376356919</v>
+        <v>487.3713351879917</v>
       </c>
       <c r="K321" t="n">
-        <v>485.2668024477001</v>
+        <v>487.5</v>
       </c>
       <c r="L321" t="n">
-        <v>485.4305328382756</v>
+        <v>487.5</v>
       </c>
     </row>
     <row r="322">
@@ -12950,22 +12950,22 @@
         <v>1.01</v>
       </c>
       <c r="G322" t="n">
-        <v>30.83094984696679</v>
+        <v>28.43853031897896</v>
       </c>
       <c r="H322" t="n">
-        <v>125.7662924166786</v>
+        <v>123.3738728886908</v>
       </c>
       <c r="I322" t="n">
-        <v>158.7965369496115</v>
+        <v>156.4041174216237</v>
       </c>
       <c r="J322" t="n">
-        <v>485.1359121115041</v>
+        <v>487.3713351879917</v>
       </c>
       <c r="K322" t="n">
-        <v>485.2645769235123</v>
+        <v>487.5</v>
       </c>
       <c r="L322" t="n">
-        <v>485.4283073140878</v>
+        <v>487.5</v>
       </c>
     </row>
     <row r="323">
@@ -12994,22 +12994,22 @@
         <v>0.44</v>
       </c>
       <c r="G323" t="n">
-        <v>25.71865883051059</v>
+        <v>23.42348908722663</v>
       </c>
       <c r="H323" t="n">
-        <v>120.6540014002224</v>
+        <v>118.3588316569384</v>
       </c>
       <c r="I323" t="n">
-        <v>153.6842459331554</v>
+        <v>151.3890761898714</v>
       </c>
       <c r="J323" t="n">
-        <v>485.1325693524928</v>
+        <v>487.3713351879917</v>
       </c>
       <c r="K323" t="n">
-        <v>485.261234164501</v>
+        <v>487.5</v>
       </c>
       <c r="L323" t="n">
-        <v>485.4249645550765</v>
+        <v>487.5</v>
       </c>
     </row>
     <row r="324">
@@ -13038,22 +13038,22 @@
         <v>0</v>
       </c>
       <c r="G324" t="n">
-        <v>32.42534140960576</v>
+        <v>30.00259218487314</v>
       </c>
       <c r="H324" t="n">
-        <v>127.3606839793176</v>
+        <v>124.937934754585</v>
       </c>
       <c r="I324" t="n">
-        <v>160.3909285122505</v>
+        <v>157.9681792875179</v>
       </c>
       <c r="J324" t="n">
-        <v>485.125637233592</v>
+        <v>487.3713351879917</v>
       </c>
       <c r="K324" t="n">
-        <v>485.2543020456002</v>
+        <v>487.5</v>
       </c>
       <c r="L324" t="n">
-        <v>485.4180324361757</v>
+        <v>487.5</v>
       </c>
     </row>
     <row r="325">
@@ -13082,22 +13082,22 @@
         <v>0.58</v>
       </c>
       <c r="G325" t="n">
-        <v>87.14415100346278</v>
+        <v>83.68050007044991</v>
       </c>
       <c r="H325" t="n">
-        <v>182.0794935731746</v>
+        <v>178.6158426401617</v>
       </c>
       <c r="I325" t="n">
-        <v>215.1097381061076</v>
+        <v>211.6460871730947</v>
       </c>
       <c r="J325" t="n">
-        <v>485.171093642098</v>
+        <v>487.3713351879917</v>
       </c>
       <c r="K325" t="n">
-        <v>485.2997584541063</v>
+        <v>487.5</v>
       </c>
       <c r="L325" t="n">
-        <v>485.4634888446818</v>
+        <v>487.5</v>
       </c>
     </row>
     <row r="326">
@@ -13126,22 +13126,22 @@
         <v>0.21</v>
       </c>
       <c r="G326" t="n">
-        <v>33.31224241995719</v>
+        <v>30.87262190757036</v>
       </c>
       <c r="H326" t="n">
-        <v>128.247584989669</v>
+        <v>125.8079644772822</v>
       </c>
       <c r="I326" t="n">
-        <v>161.277829522602</v>
+        <v>158.8382090102151</v>
       </c>
       <c r="J326" t="n">
-        <v>485.3711177966874</v>
+        <v>487.3713351879917</v>
       </c>
       <c r="K326" t="n">
-        <v>485.4997826086957</v>
+        <v>487.5</v>
       </c>
       <c r="L326" t="n">
-        <v>485.6635129992712</v>
+        <v>487.5</v>
       </c>
     </row>
     <row r="327">
@@ -13170,22 +13170,22 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="G327" t="n">
-        <v>22.05118332062044</v>
+        <v>19.82577901177584</v>
       </c>
       <c r="H327" t="n">
-        <v>116.9865258903323</v>
+        <v>114.7611215814877</v>
       </c>
       <c r="I327" t="n">
-        <v>150.0167704232652</v>
+        <v>147.7913661144206</v>
       </c>
       <c r="J327" t="n">
-        <v>485.5711419512768</v>
+        <v>487.3713351879917</v>
       </c>
       <c r="K327" t="n">
-        <v>485.699806763285</v>
+        <v>487.5</v>
       </c>
       <c r="L327" t="n">
-        <v>485.8635371538605</v>
+        <v>487.5</v>
       </c>
     </row>
     <row r="328">
@@ -13214,22 +13214,22 @@
         <v>0.17</v>
       </c>
       <c r="G328" t="n">
-        <v>14.98560460497663</v>
+        <v>12.89460696560621</v>
       </c>
       <c r="H328" t="n">
-        <v>109.9209471746885</v>
+        <v>107.829949535318</v>
       </c>
       <c r="I328" t="n">
-        <v>142.9511917076214</v>
+        <v>140.860194068251</v>
       </c>
       <c r="J328" t="n">
-        <v>485.7711661058661</v>
+        <v>487.3713351879917</v>
       </c>
       <c r="K328" t="n">
-        <v>485.8998309178744</v>
+        <v>487.5</v>
       </c>
       <c r="L328" t="n">
-        <v>486.0635613084499</v>
+        <v>487.5</v>
       </c>
     </row>
     <row r="329">
@@ -13261,19 +13261,19 @@
         <v>0</v>
       </c>
       <c r="H329" t="n">
-        <v>93.90863770505879</v>
+        <v>92.12223807145932</v>
       </c>
       <c r="I329" t="n">
-        <v>126.9388822379917</v>
+        <v>125.1524826043923</v>
       </c>
       <c r="J329" t="n">
-        <v>485.9711902604556</v>
+        <v>487.3713351879917</v>
       </c>
       <c r="K329" t="n">
-        <v>486.0998550724638</v>
+        <v>487.5</v>
       </c>
       <c r="L329" t="n">
-        <v>486.2635854630393</v>
+        <v>487.5</v>
       </c>
     </row>
     <row r="330">
@@ -13305,19 +13305,19 @@
         <v>0</v>
       </c>
       <c r="H330" t="n">
-        <v>87.02973046542697</v>
+        <v>85.37418649827895</v>
       </c>
       <c r="I330" t="n">
-        <v>120.0599749983599</v>
+        <v>118.4044310312119</v>
       </c>
       <c r="J330" t="n">
-        <v>486.1712144150449</v>
+        <v>487.3713351879917</v>
       </c>
       <c r="K330" t="n">
-        <v>486.2998792270532</v>
+        <v>487.5</v>
       </c>
       <c r="L330" t="n">
-        <v>486.4636096176287</v>
+        <v>487.5</v>
       </c>
     </row>
     <row r="331">
@@ -13346,22 +13346,22 @@
         <v>0.23</v>
       </c>
       <c r="G331" t="n">
-        <v>16.41905036575042</v>
+        <v>14.30078465983777</v>
       </c>
       <c r="H331" t="n">
-        <v>111.3543929354622</v>
+        <v>109.2361272295496</v>
       </c>
       <c r="I331" t="n">
-        <v>144.3846374683952</v>
+        <v>142.2663717624825</v>
       </c>
       <c r="J331" t="n">
-        <v>486.3712385696343</v>
+        <v>487.3585392748581</v>
       </c>
       <c r="K331" t="n">
-        <v>486.4999033816425</v>
+        <v>487.4872040868664</v>
       </c>
       <c r="L331" t="n">
-        <v>486.663633772218</v>
+        <v>487.5</v>
       </c>
     </row>
     <row r="332">
@@ -13390,22 +13390,22 @@
         <v>0</v>
       </c>
       <c r="G332" t="n">
-        <v>33.6162546582581</v>
+        <v>31.17085099999268</v>
       </c>
       <c r="H332" t="n">
-        <v>128.5515972279699</v>
+        <v>126.1061935697045</v>
       </c>
       <c r="I332" t="n">
-        <v>161.5818417609029</v>
+        <v>159.1364381026374</v>
       </c>
       <c r="J332" t="n">
-        <v>486.5712627242236</v>
+        <v>487.3160023059956</v>
       </c>
       <c r="K332" t="n">
-        <v>486.6999275362319</v>
+        <v>487.4446671180038</v>
       </c>
       <c r="L332" t="n">
-        <v>486.8636579268074</v>
+        <v>487.5</v>
       </c>
     </row>
     <row r="333">
@@ -13434,22 +13434,22 @@
         <v>0.04</v>
       </c>
       <c r="G333" t="n">
-        <v>35.54917694255207</v>
+        <v>33.5681652014232</v>
       </c>
       <c r="H333" t="n">
-        <v>130.4845195122639</v>
+        <v>128.503507771135</v>
       </c>
       <c r="I333" t="n">
-        <v>163.5147640451968</v>
+        <v>161.533752304068</v>
       </c>
       <c r="J333" t="n">
-        <v>486.771286878813</v>
+        <v>487.2859319754552</v>
       </c>
       <c r="K333" t="n">
-        <v>486.8999516908212</v>
+        <v>487.4145967874634</v>
       </c>
       <c r="L333" t="n">
-        <v>487.0636820813967</v>
+        <v>487.5</v>
       </c>
     </row>
     <row r="334">
@@ -13478,22 +13478,22 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="G334" t="n">
-        <v>43.47043805047633</v>
+        <v>41.83223132424922</v>
       </c>
       <c r="H334" t="n">
-        <v>138.4057806201882</v>
+        <v>136.767573893961</v>
       </c>
       <c r="I334" t="n">
-        <v>171.4360251531211</v>
+        <v>169.797818426894</v>
       </c>
       <c r="J334" t="n">
-        <v>486.9713110334024</v>
+        <v>487.2662788479802</v>
       </c>
       <c r="K334" t="n">
-        <v>487.0999758454107</v>
+        <v>487.3949436599885</v>
       </c>
       <c r="L334" t="n">
-        <v>487.2637062359861</v>
+        <v>487.5</v>
       </c>
     </row>
     <row r="335">
@@ -13522,22 +13522,22 @@
         <v>0</v>
       </c>
       <c r="G335" t="n">
-        <v>85.98143326598407</v>
+        <v>84.37205320815491</v>
       </c>
       <c r="H335" t="n">
-        <v>180.9167758356959</v>
+        <v>179.3073957778667</v>
       </c>
       <c r="I335" t="n">
-        <v>213.9470203686288</v>
+        <v>212.3376403107997</v>
       </c>
       <c r="J335" t="n">
-        <v>487.1713351879918</v>
+        <v>487.2708516345662</v>
       </c>
       <c r="K335" t="n">
-        <v>487.3</v>
+        <v>487.3995164465745</v>
       </c>
       <c r="L335" t="n">
-        <v>487.4637303905755</v>
+        <v>487.5</v>
       </c>
     </row>
     <row r="336">
@@ -13566,22 +13566,22 @@
         <v>0.12</v>
       </c>
       <c r="G336" t="n">
-        <v>177.4165291975804</v>
+        <v>176.1673201264873</v>
       </c>
       <c r="H336" t="n">
-        <v>198.57463950332</v>
+        <v>197.3254304322269</v>
       </c>
       <c r="I336" t="n">
-        <v>213.0134071688172</v>
+        <v>211.7641980977241</v>
       </c>
       <c r="J336" t="n">
-        <v>487.190530191585</v>
+        <v>487.2939660788703</v>
       </c>
       <c r="K336" t="n">
-        <v>487.3048387096774</v>
+        <v>487.4082745969628</v>
       </c>
       <c r="L336" t="n">
-        <v>487.3759970439641</v>
+        <v>487.4794329312494</v>
       </c>
     </row>
     <row r="337">
@@ -13610,22 +13610,22 @@
         <v>0.04</v>
       </c>
       <c r="G337" t="n">
-        <v>161.0971855032539</v>
+        <v>160.3741021929512</v>
       </c>
       <c r="H337" t="n">
-        <v>182.2552958089935</v>
+        <v>181.5322124986907</v>
       </c>
       <c r="I337" t="n">
-        <v>196.6940634744907</v>
+        <v>195.9709801641879</v>
       </c>
       <c r="J337" t="n">
-        <v>487.1953689012624</v>
+        <v>487.3040716430105</v>
       </c>
       <c r="K337" t="n">
-        <v>487.3096774193548</v>
+        <v>487.418380161103</v>
       </c>
       <c r="L337" t="n">
-        <v>487.3808357536415</v>
+        <v>487.4895384953896</v>
       </c>
     </row>
     <row r="338">
@@ -13654,22 +13654,22 @@
         <v>0.4</v>
       </c>
       <c r="G338" t="n">
-        <v>158.1488577411477</v>
+        <v>157.8113901972895</v>
       </c>
       <c r="H338" t="n">
-        <v>179.3069680468872</v>
+        <v>178.969500503029</v>
       </c>
       <c r="I338" t="n">
-        <v>193.7457357123845</v>
+        <v>193.4082681685262</v>
       </c>
       <c r="J338" t="n">
-        <v>487.2002076109398</v>
+        <v>487.3084754258438</v>
       </c>
       <c r="K338" t="n">
-        <v>487.3145161290323</v>
+        <v>487.4227839439362</v>
       </c>
       <c r="L338" t="n">
-        <v>487.3856744633189</v>
+        <v>487.4939422782229</v>
       </c>
     </row>
     <row r="339">
@@ -13698,7 +13698,7 @@
         <v>0.15</v>
       </c>
       <c r="G339" t="n">
-        <v>146.426289762277</v>
+        <v>146.4262897622771</v>
       </c>
       <c r="H339" t="n">
         <v>167.5844000680166</v>
@@ -13707,13 +13707,13 @@
         <v>182.0231677335138</v>
       </c>
       <c r="J339" t="n">
-        <v>487.2050463206172</v>
+        <v>487.3265857045</v>
       </c>
       <c r="K339" t="n">
-        <v>487.3193548387097</v>
+        <v>487.4408942225924</v>
       </c>
       <c r="L339" t="n">
-        <v>487.3905131729964</v>
+        <v>487.5</v>
       </c>
     </row>
     <row r="340">
@@ -13751,13 +13751,13 @@
         <v>173.6177857703116</v>
       </c>
       <c r="J340" t="n">
-        <v>487.2098850302946</v>
+        <v>487.337291151444</v>
       </c>
       <c r="K340" t="n">
-        <v>487.3241935483871</v>
+        <v>487.4515996695364</v>
       </c>
       <c r="L340" t="n">
-        <v>487.3953518826738</v>
+        <v>487.5</v>
       </c>
     </row>
     <row r="341">
@@ -13795,13 +13795,13 @@
         <v>161.092629645667</v>
       </c>
       <c r="J341" t="n">
-        <v>487.214723739972</v>
+        <v>487.3447937533502</v>
       </c>
       <c r="K341" t="n">
-        <v>487.3290322580645</v>
+        <v>487.4591022714427</v>
       </c>
       <c r="L341" t="n">
-        <v>487.4001905923512</v>
+        <v>487.5</v>
       </c>
     </row>
     <row r="342">
@@ -13839,13 +13839,13 @@
         <v>146.0772105167255</v>
       </c>
       <c r="J342" t="n">
-        <v>487.2195624496495</v>
+        <v>487.3474874019798</v>
       </c>
       <c r="K342" t="n">
-        <v>487.3338709677419</v>
+        <v>487.4617959200722</v>
       </c>
       <c r="L342" t="n">
-        <v>487.4050293020286</v>
+        <v>487.5</v>
       </c>
     </row>
     <row r="343">
@@ -13883,13 +13883,13 @@
         <v>146.2854873681032</v>
       </c>
       <c r="J343" t="n">
-        <v>487.2244011593269</v>
+        <v>487.3413824083389</v>
       </c>
       <c r="K343" t="n">
-        <v>487.3387096774194</v>
+        <v>487.4556909264313</v>
       </c>
       <c r="L343" t="n">
-        <v>487.4098680117061</v>
+        <v>487.5</v>
       </c>
     </row>
     <row r="344">
@@ -13927,13 +13927,13 @@
         <v>133.1061388822785</v>
       </c>
       <c r="J344" t="n">
-        <v>487.2292398690043</v>
+        <v>487.3213720908545</v>
       </c>
       <c r="K344" t="n">
-        <v>487.3435483870968</v>
+        <v>487.435680608947</v>
       </c>
       <c r="L344" t="n">
-        <v>487.4147067213835</v>
+        <v>487.5</v>
       </c>
     </row>
     <row r="345">
@@ -13962,7 +13962,7 @@
         <v>0</v>
       </c>
       <c r="G345" t="n">
-        <v>88.46231537354475</v>
+        <v>88.46231537354478</v>
       </c>
       <c r="H345" t="n">
         <v>109.6204256792843</v>
@@ -13971,13 +13971,13 @@
         <v>124.0591933447815</v>
       </c>
       <c r="J345" t="n">
-        <v>487.2340785786818</v>
+        <v>487.2964888692742</v>
       </c>
       <c r="K345" t="n">
-        <v>487.3483870967742</v>
+        <v>487.4107973873667</v>
       </c>
       <c r="L345" t="n">
-        <v>487.4195454310609</v>
+        <v>487.4819557216534</v>
       </c>
     </row>
     <row r="346">
@@ -14015,13 +14015,13 @@
         <v>117.5645706709859</v>
       </c>
       <c r="J346" t="n">
-        <v>487.2389172883592</v>
+        <v>487.2829721833895</v>
       </c>
       <c r="K346" t="n">
-        <v>487.3532258064516</v>
+        <v>487.3972807014819</v>
       </c>
       <c r="L346" t="n">
-        <v>487.4243841407383</v>
+        <v>487.4684390357686</v>
       </c>
     </row>
     <row r="347">
@@ -14050,7 +14050,7 @@
         <v>0.08</v>
       </c>
       <c r="G347" t="n">
-        <v>78.90697522702837</v>
+        <v>78.9069752270284</v>
       </c>
       <c r="H347" t="n">
         <v>100.0650855327679</v>
@@ -14059,13 +14059,13 @@
         <v>114.5038531982651</v>
       </c>
       <c r="J347" t="n">
-        <v>487.2437559980366</v>
+        <v>487.2860274290094</v>
       </c>
       <c r="K347" t="n">
-        <v>487.358064516129</v>
+        <v>487.4003359471019</v>
       </c>
       <c r="L347" t="n">
-        <v>487.4292228504157</v>
+        <v>487.4714942813886</v>
       </c>
     </row>
     <row r="348">
@@ -14103,13 +14103,13 @@
         <v>132.9133025487564</v>
       </c>
       <c r="J348" t="n">
-        <v>487.248594707714</v>
+        <v>487.2896954137697</v>
       </c>
       <c r="K348" t="n">
-        <v>487.3629032258065</v>
+        <v>487.4040039318622</v>
       </c>
       <c r="L348" t="n">
-        <v>487.4340615600931</v>
+        <v>487.4751622661489</v>
       </c>
     </row>
     <row r="349">
@@ -14138,7 +14138,7 @@
         <v>0.09</v>
       </c>
       <c r="G349" t="n">
-        <v>91.89269292352103</v>
+        <v>91.89269292352105</v>
       </c>
       <c r="H349" t="n">
         <v>113.0508032292606</v>
@@ -14147,13 +14147,13 @@
         <v>127.4895708947578</v>
       </c>
       <c r="J349" t="n">
-        <v>487.2534334173914</v>
+        <v>487.2891567949633</v>
       </c>
       <c r="K349" t="n">
-        <v>487.3677419354839</v>
+        <v>487.4034653130558</v>
       </c>
       <c r="L349" t="n">
-        <v>487.4389002697706</v>
+        <v>487.4746236473425</v>
       </c>
     </row>
     <row r="350">
@@ -14182,7 +14182,7 @@
         <v>0</v>
       </c>
       <c r="G350" t="n">
-        <v>91.65861638289431</v>
+        <v>91.65861638289434</v>
       </c>
       <c r="H350" t="n">
         <v>112.8167266886339</v>
@@ -14191,13 +14191,13 @@
         <v>127.2554943541311</v>
       </c>
       <c r="J350" t="n">
-        <v>487.2582721270688</v>
+        <v>487.294483123128</v>
       </c>
       <c r="K350" t="n">
-        <v>487.3725806451613</v>
+        <v>487.4087916412204</v>
       </c>
       <c r="L350" t="n">
-        <v>487.443738979448</v>
+        <v>487.4799499755071</v>
       </c>
     </row>
     <row r="351">
@@ -14235,13 +14235,13 @@
         <v>132.1675352749737</v>
       </c>
       <c r="J351" t="n">
-        <v>487.2631108367463</v>
+        <v>487.2902375401038</v>
       </c>
       <c r="K351" t="n">
-        <v>487.3774193548387</v>
+        <v>487.4045460581963</v>
       </c>
       <c r="L351" t="n">
-        <v>487.4485776891254</v>
+        <v>487.475704392483</v>
       </c>
     </row>
     <row r="352">
@@ -14270,7 +14270,7 @@
         <v>0</v>
       </c>
       <c r="G352" t="n">
-        <v>87.01743488587223</v>
+        <v>87.01743488587229</v>
       </c>
       <c r="H352" t="n">
         <v>108.1755451916118</v>
@@ -14279,13 +14279,13 @@
         <v>122.614312857109</v>
       </c>
       <c r="J352" t="n">
-        <v>487.2679495464237</v>
+        <v>487.2787777084161</v>
       </c>
       <c r="K352" t="n">
-        <v>487.3822580645161</v>
+        <v>487.3930862265086</v>
       </c>
       <c r="L352" t="n">
-        <v>487.4534163988028</v>
+        <v>487.4642445607952</v>
       </c>
     </row>
     <row r="353">
@@ -14323,13 +14323,13 @@
         <v>118.4024054289851</v>
       </c>
       <c r="J353" t="n">
-        <v>487.2727882561011</v>
+        <v>487.2735093711127</v>
       </c>
       <c r="K353" t="n">
-        <v>487.3870967741935</v>
+        <v>487.3878178892052</v>
       </c>
       <c r="L353" t="n">
-        <v>487.4582551084802</v>
+        <v>487.4589762234918</v>
       </c>
     </row>
     <row r="354">
@@ -14361,7 +14361,7 @@
         <v>77.83147328228614</v>
       </c>
       <c r="H354" t="n">
-        <v>98.98958358802568</v>
+        <v>98.9895835880257</v>
       </c>
       <c r="I354" t="n">
         <v>113.4283512535229</v>
@@ -14402,10 +14402,10 @@
         <v>0</v>
       </c>
       <c r="G355" t="n">
-        <v>75.77067103057615</v>
+        <v>75.77067103057618</v>
       </c>
       <c r="H355" t="n">
-        <v>96.92878133631571</v>
+        <v>96.92878133631572</v>
       </c>
       <c r="I355" t="n">
         <v>111.3675490018129</v>
@@ -14581,7 +14581,7 @@
         <v>66.97995747655045</v>
       </c>
       <c r="H359" t="n">
-        <v>88.13806778228999</v>
+        <v>88.13806778229001</v>
       </c>
       <c r="I359" t="n">
         <v>102.5768354477872</v>
@@ -14622,22 +14622,22 @@
         <v>0</v>
       </c>
       <c r="G360" t="n">
-        <v>66.04991653624953</v>
+        <v>66.04991653624955</v>
       </c>
       <c r="H360" t="n">
-        <v>87.20802684198908</v>
+        <v>87.2080268419891</v>
       </c>
       <c r="I360" t="n">
         <v>101.6467945074863</v>
       </c>
       <c r="J360" t="n">
-        <v>487.306659223843</v>
+        <v>487.3075736907791</v>
       </c>
       <c r="K360" t="n">
-        <v>487.4209677419355</v>
+        <v>487.4218822088716</v>
       </c>
       <c r="L360" t="n">
-        <v>487.4921260762222</v>
+        <v>487.4930405431583</v>
       </c>
     </row>
     <row r="361">
@@ -14666,22 +14666,22 @@
         <v>0</v>
       </c>
       <c r="G361" t="n">
-        <v>66.80279943701876</v>
+        <v>66.80279943701879</v>
       </c>
       <c r="H361" t="n">
-        <v>87.96090974275832</v>
+        <v>87.96090974275835</v>
       </c>
       <c r="I361" t="n">
-        <v>102.3996774082555</v>
+        <v>102.3996774082556</v>
       </c>
       <c r="J361" t="n">
-        <v>487.3114979335205</v>
+        <v>487.3236184470642</v>
       </c>
       <c r="K361" t="n">
-        <v>487.4258064516129</v>
+        <v>487.4379269651566</v>
       </c>
       <c r="L361" t="n">
-        <v>487.4969647858996</v>
+        <v>487.5</v>
       </c>
     </row>
     <row r="362">
@@ -14719,10 +14719,10 @@
         <v>98.99361400589552</v>
       </c>
       <c r="J362" t="n">
-        <v>487.3163366431979</v>
+        <v>487.3403999653495</v>
       </c>
       <c r="K362" t="n">
-        <v>487.4306451612903</v>
+        <v>487.454708483442</v>
       </c>
       <c r="L362" t="n">
         <v>487.5</v>
@@ -14763,10 +14763,10 @@
         <v>99.16943255549252</v>
       </c>
       <c r="J363" t="n">
-        <v>487.3211753528753</v>
+        <v>487.3445208505857</v>
       </c>
       <c r="K363" t="n">
-        <v>487.4354838709677</v>
+        <v>487.4588293686782</v>
       </c>
       <c r="L363" t="n">
         <v>487.5</v>
@@ -14801,16 +14801,16 @@
         <v>65.59130304806573</v>
       </c>
       <c r="H364" t="n">
-        <v>86.74941335380527</v>
+        <v>86.74941335380528</v>
       </c>
       <c r="I364" t="n">
         <v>101.1881810193025</v>
       </c>
       <c r="J364" t="n">
-        <v>487.3260140625527</v>
+        <v>487.3432216492918</v>
       </c>
       <c r="K364" t="n">
-        <v>487.4403225806452</v>
+        <v>487.4575301673843</v>
       </c>
       <c r="L364" t="n">
         <v>487.5</v>
@@ -14842,19 +14842,19 @@
         <v>0</v>
       </c>
       <c r="G365" t="n">
-        <v>76.8206006748766</v>
+        <v>76.82060067487663</v>
       </c>
       <c r="H365" t="n">
-        <v>97.97871098061616</v>
+        <v>97.97871098061617</v>
       </c>
       <c r="I365" t="n">
         <v>112.4174786461134</v>
       </c>
       <c r="J365" t="n">
-        <v>487.3308527722301</v>
+        <v>487.3470319361849</v>
       </c>
       <c r="K365" t="n">
-        <v>487.4451612903226</v>
+        <v>487.4613404542773</v>
       </c>
       <c r="L365" t="n">
         <v>487.5</v>
@@ -14886,19 +14886,19 @@
         <v>0</v>
       </c>
       <c r="G366" t="n">
-        <v>73.25625323095809</v>
+        <v>73.25625323095812</v>
       </c>
       <c r="H366" t="n">
-        <v>94.41436353669765</v>
+        <v>94.41436353669766</v>
       </c>
       <c r="I366" t="n">
         <v>108.8531312021949</v>
       </c>
       <c r="J366" t="n">
-        <v>487.3356914819075</v>
+        <v>487.3449295585881</v>
       </c>
       <c r="K366" t="n">
-        <v>487.45</v>
+        <v>487.4592380766806</v>
       </c>
       <c r="L366" t="n">
         <v>487.5</v>
@@ -25348,22 +25348,22 @@
         <v>6.14</v>
       </c>
       <c r="G641" t="n">
-        <v>280.2192333213206</v>
+        <v>281.1709241425767</v>
       </c>
       <c r="H641" t="n">
-        <v>304.2222222222222</v>
+        <v>305.1739130434783</v>
       </c>
       <c r="I641" t="n">
-        <v>330.6420844174584</v>
+        <v>331.5937752387144</v>
       </c>
       <c r="J641" t="n">
-        <v>410.8369792130136</v>
+        <v>410.7139357347527</v>
       </c>
       <c r="K641" t="n">
-        <v>411.56</v>
+        <v>411.4369565217391</v>
       </c>
       <c r="L641" t="n">
-        <v>412.1924941210731</v>
+        <v>412.0694506428122</v>
       </c>
     </row>
     <row r="642">
@@ -25377,7 +25377,7 @@
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2021_2019_2018_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D642" t="n">
@@ -25392,22 +25392,22 @@
         <v>4.85</v>
       </c>
       <c r="G642" t="n">
-        <v>256.7699744146008</v>
+        <v>328.7886777657651</v>
       </c>
       <c r="H642" t="n">
-        <v>280.7729633155024</v>
+        <v>352.7916666666667</v>
       </c>
       <c r="I642" t="n">
-        <v>307.1928255107385</v>
+        <v>379.2115288619028</v>
       </c>
       <c r="J642" t="n">
-        <v>410.9227142344191</v>
+        <v>410.8315625463469</v>
       </c>
       <c r="K642" t="n">
-        <v>411.6457350214055</v>
+        <v>411.5545833333333</v>
       </c>
       <c r="L642" t="n">
-        <v>412.2782291424786</v>
+        <v>412.1870774544064</v>
       </c>
     </row>
     <row r="643">
@@ -25421,7 +25421,7 @@
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2021_2019_2018_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D643" t="n">
@@ -25436,22 +25436,22 @@
         <v>6.28</v>
       </c>
       <c r="G643" t="n">
-        <v>236.4744512482103</v>
+        <v>293.5803444324317</v>
       </c>
       <c r="H643" t="n">
-        <v>260.4774401491119</v>
+        <v>317.5833333333333</v>
       </c>
       <c r="I643" t="n">
-        <v>286.897302344348</v>
+        <v>344.0031955285694</v>
       </c>
       <c r="J643" t="n">
-        <v>410.9046378879251</v>
+        <v>410.7153125463469</v>
       </c>
       <c r="K643" t="n">
-        <v>411.6276586749115</v>
+        <v>411.4383333333333</v>
       </c>
       <c r="L643" t="n">
-        <v>412.2601527959847</v>
+        <v>412.0708274544065</v>
       </c>
     </row>
     <row r="644">
@@ -25465,7 +25465,7 @@
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2021_2019_2018_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D644" t="n">
@@ -25480,22 +25480,22 @@
         <v>4.19</v>
       </c>
       <c r="G644" t="n">
-        <v>214.8155564083613</v>
+        <v>296.9061020081894</v>
       </c>
       <c r="H644" t="n">
-        <v>238.8185453092629</v>
+        <v>320.9090909090909</v>
       </c>
       <c r="I644" t="n">
-        <v>265.238407504499</v>
+        <v>347.3289531043271</v>
       </c>
       <c r="J644" t="n">
-        <v>410.8761729289131</v>
+        <v>410.92561557665</v>
       </c>
       <c r="K644" t="n">
-        <v>411.5991937158996</v>
+        <v>411.6486363636364</v>
       </c>
       <c r="L644" t="n">
-        <v>412.2316878369727</v>
+        <v>412.2811304847095</v>
       </c>
     </row>
     <row r="645">
@@ -25509,7 +25509,7 @@
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2021_2019_2018_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D645" t="n">
@@ -25524,22 +25524,22 @@
         <v>4.26</v>
       </c>
       <c r="G645" t="n">
-        <v>195.44585407053</v>
+        <v>307.8205405108631</v>
       </c>
       <c r="H645" t="n">
-        <v>219.4488429714316</v>
+        <v>331.8235294117647</v>
       </c>
       <c r="I645" t="n">
-        <v>245.8687051666677</v>
+        <v>358.2433916070008</v>
       </c>
       <c r="J645" t="n">
-        <v>410.8689081539133</v>
+        <v>411.10933215419</v>
       </c>
       <c r="K645" t="n">
-        <v>411.5919289408997</v>
+        <v>411.8323529411765</v>
       </c>
       <c r="L645" t="n">
-        <v>412.2244230619729</v>
+        <v>412.4648470622496</v>
       </c>
     </row>
     <row r="646">
@@ -25553,7 +25553,7 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2021_2019_2018_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D646" t="n">
@@ -25568,22 +25568,22 @@
         <v>2.77</v>
       </c>
       <c r="G646" t="n">
-        <v>187.1965856188878</v>
+        <v>282.7886777657651</v>
       </c>
       <c r="H646" t="n">
-        <v>211.1995745197894</v>
+        <v>306.7916666666667</v>
       </c>
       <c r="I646" t="n">
-        <v>237.6194367150256</v>
+        <v>333.2115288619028</v>
       </c>
       <c r="J646" t="n">
-        <v>410.879145494012</v>
+        <v>411.0898958796803</v>
       </c>
       <c r="K646" t="n">
-        <v>411.6021662809984</v>
+        <v>411.8129166666667</v>
       </c>
       <c r="L646" t="n">
-        <v>412.2346604020715</v>
+        <v>412.4454107877398</v>
       </c>
     </row>
     <row r="647">
@@ -25597,7 +25597,7 @@
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2021_2019_2018_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D647" t="n">
@@ -25612,22 +25612,22 @@
         <v>4.55</v>
       </c>
       <c r="G647" t="n">
-        <v>186.570415024004</v>
+        <v>271.9136777657651</v>
       </c>
       <c r="H647" t="n">
-        <v>210.5734039249056</v>
+        <v>295.9166666666667</v>
       </c>
       <c r="I647" t="n">
-        <v>236.9932661201418</v>
+        <v>322.3365288619028</v>
       </c>
       <c r="J647" t="n">
-        <v>411.051060733037</v>
+        <v>410.7469792130136</v>
       </c>
       <c r="K647" t="n">
-        <v>411.7740815200234</v>
+        <v>411.47</v>
       </c>
       <c r="L647" t="n">
-        <v>412.4065756410965</v>
+        <v>412.1024941210732</v>
       </c>
     </row>
     <row r="648">
@@ -25641,7 +25641,7 @@
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2021_2019_2018_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D648" t="n">
@@ -25656,22 +25656,22 @@
         <v>5.05</v>
       </c>
       <c r="G648" t="n">
-        <v>191.0564770095784</v>
+        <v>290.1220110990984</v>
       </c>
       <c r="H648" t="n">
-        <v>215.05946591048</v>
+        <v>314.125</v>
       </c>
       <c r="I648" t="n">
-        <v>241.4793281057161</v>
+        <v>340.5448621952361</v>
       </c>
       <c r="J648" t="n">
-        <v>411.0589096135415</v>
+        <v>410.5486458796803</v>
       </c>
       <c r="K648" t="n">
-        <v>411.7819304005279</v>
+        <v>411.2716666666667</v>
       </c>
       <c r="L648" t="n">
-        <v>412.4144245216011</v>
+        <v>411.9041607877398</v>
       </c>
     </row>
     <row r="649">
@@ -25685,7 +25685,7 @@
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2021_2019_2018_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D649" t="n">
@@ -25700,22 +25700,22 @@
         <v>2.54</v>
       </c>
       <c r="G649" t="n">
-        <v>187.9666149344257</v>
+        <v>323.7470110990984</v>
       </c>
       <c r="H649" t="n">
-        <v>211.9696038353273</v>
+        <v>347.75</v>
       </c>
       <c r="I649" t="n">
-        <v>238.3894660305634</v>
+        <v>374.1698621952361</v>
       </c>
       <c r="J649" t="n">
-        <v>411.0612853343967</v>
+        <v>410.6715625463469</v>
       </c>
       <c r="K649" t="n">
-        <v>411.7843061213831</v>
+        <v>411.3945833333333</v>
       </c>
       <c r="L649" t="n">
-        <v>412.4168002424562</v>
+        <v>412.0270774544064</v>
       </c>
     </row>
     <row r="650">
@@ -25729,7 +25729,7 @@
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2021_2019_2018_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D650" t="n">
@@ -25744,22 +25744,22 @@
         <v>4.45</v>
       </c>
       <c r="G650" t="n">
-        <v>181.8561358021512</v>
+        <v>324.6636777657651</v>
       </c>
       <c r="H650" t="n">
-        <v>205.8591247030528</v>
+        <v>348.6666666666667</v>
       </c>
       <c r="I650" t="n">
-        <v>232.2789868982889</v>
+        <v>375.0865288619028</v>
       </c>
       <c r="J650" t="n">
-        <v>411.0675905424198</v>
+        <v>410.7432292130136</v>
       </c>
       <c r="K650" t="n">
-        <v>411.7906113294062</v>
+        <v>411.46625</v>
       </c>
       <c r="L650" t="n">
-        <v>412.4231054504793</v>
+        <v>412.0987441210731</v>
       </c>
     </row>
     <row r="651">
@@ -25773,7 +25773,7 @@
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2021_2019_2018_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D651" t="n">
@@ -25788,22 +25788,22 @@
         <v>1.91</v>
       </c>
       <c r="G651" t="n">
-        <v>179.6907697783022</v>
+        <v>346.5803444324317</v>
       </c>
       <c r="H651" t="n">
-        <v>203.6937586792038</v>
+        <v>370.5833333333333</v>
       </c>
       <c r="I651" t="n">
-        <v>230.11362087444</v>
+        <v>397.0031955285694</v>
       </c>
       <c r="J651" t="n">
-        <v>411.0678857824891</v>
+        <v>410.8944792130136</v>
       </c>
       <c r="K651" t="n">
-        <v>411.7909065694755</v>
+        <v>411.6175</v>
       </c>
       <c r="L651" t="n">
-        <v>412.4234006905486</v>
+        <v>412.2499941210731</v>
       </c>
     </row>
     <row r="652">
@@ -25817,7 +25817,7 @@
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2021_2019_2018_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D652" t="n">
@@ -25832,22 +25832,22 @@
         <v>5.84</v>
       </c>
       <c r="G652" t="n">
-        <v>183.4329449029186</v>
+        <v>339.8606474627348</v>
       </c>
       <c r="H652" t="n">
-        <v>207.4359338038201</v>
+        <v>363.8636363636364</v>
       </c>
       <c r="I652" t="n">
-        <v>233.8557959990563</v>
+        <v>390.2834985588725</v>
       </c>
       <c r="J652" t="n">
-        <v>410.8637150068479</v>
+        <v>411.08561557665</v>
       </c>
       <c r="K652" t="n">
-        <v>411.5867357938344</v>
+        <v>411.8086363636364</v>
       </c>
       <c r="L652" t="n">
-        <v>412.2192299149075</v>
+        <v>412.4411304847096</v>
       </c>
     </row>
     <row r="653">
@@ -25861,7 +25861,7 @@
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2021_2019_2018_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D653" t="n">
@@ -25876,22 +25876,22 @@
         <v>5.46</v>
       </c>
       <c r="G653" t="n">
-        <v>179.463118750138</v>
+        <v>329.1274458817071</v>
       </c>
       <c r="H653" t="n">
-        <v>203.4661076510396</v>
+        <v>353.1304347826087</v>
       </c>
       <c r="I653" t="n">
-        <v>229.8859698462757</v>
+        <v>379.5502969778448</v>
       </c>
       <c r="J653" t="n">
-        <v>410.8337087510217</v>
+        <v>411.0526313869266</v>
       </c>
       <c r="K653" t="n">
-        <v>411.5567295380081</v>
+        <v>411.775652173913</v>
       </c>
       <c r="L653" t="n">
-        <v>412.1892236590813</v>
+        <v>412.4081462949862</v>
       </c>
     </row>
     <row r="654">
@@ -25905,7 +25905,7 @@
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2021_2019_2018_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D654" t="n">
@@ -25920,22 +25920,22 @@
         <v>5.22</v>
       </c>
       <c r="G654" t="n">
-        <v>180.933286234582</v>
+        <v>350.9970110990984</v>
       </c>
       <c r="H654" t="n">
-        <v>204.9362751354836</v>
+        <v>375</v>
       </c>
       <c r="I654" t="n">
-        <v>231.3561373307198</v>
+        <v>401.4198621952361</v>
       </c>
       <c r="J654" t="n">
-        <v>410.7639055639582</v>
+        <v>411.1174139956223</v>
       </c>
       <c r="K654" t="n">
-        <v>411.4869263509446</v>
+        <v>411.8404347826087</v>
       </c>
       <c r="L654" t="n">
-        <v>412.1194204720177</v>
+        <v>412.4729289036818</v>
       </c>
     </row>
     <row r="655">
@@ -25949,7 +25949,7 @@
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2021_2019_2018_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D655" t="n">
@@ -25964,22 +25964,22 @@
         <v>4.97</v>
       </c>
       <c r="G655" t="n">
-        <v>186.7017685820532</v>
+        <v>323.4414555435429</v>
       </c>
       <c r="H655" t="n">
-        <v>210.7047574829548</v>
+        <v>347.4444444444445</v>
       </c>
       <c r="I655" t="n">
-        <v>237.1246196781909</v>
+        <v>373.8643066396806</v>
       </c>
       <c r="J655" t="n">
-        <v>410.7537509180277</v>
+        <v>410.9908681019025</v>
       </c>
       <c r="K655" t="n">
-        <v>411.4767717050141</v>
+        <v>411.7138888888889</v>
       </c>
       <c r="L655" t="n">
-        <v>412.1092658260873</v>
+        <v>412.346383009962</v>
       </c>
     </row>
     <row r="656">
@@ -25993,7 +25993,7 @@
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2021_2019_2018_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D656" t="n">
@@ -26008,22 +26008,22 @@
         <v>3.19</v>
       </c>
       <c r="G656" t="n">
-        <v>189.1501180614385</v>
+        <v>302.1220110990984</v>
       </c>
       <c r="H656" t="n">
-        <v>213.15310696234</v>
+        <v>326.125</v>
       </c>
       <c r="I656" t="n">
-        <v>239.5729691575762</v>
+        <v>352.5448621952361</v>
       </c>
       <c r="J656" t="n">
-        <v>410.7389606909425</v>
+        <v>410.7765625463469</v>
       </c>
       <c r="K656" t="n">
-        <v>411.4619814779289</v>
+        <v>411.4995833333333</v>
       </c>
       <c r="L656" t="n">
-        <v>412.0944755990021</v>
+        <v>412.1320774544064</v>
       </c>
     </row>
     <row r="657">
@@ -26037,7 +26037,7 @@
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2021_2019_2018_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D657" t="n">
@@ -26052,22 +26052,22 @@
         <v>3.02</v>
       </c>
       <c r="G657" t="n">
-        <v>190.2570203811595</v>
+        <v>304.3720110990984</v>
       </c>
       <c r="H657" t="n">
-        <v>214.2600092820611</v>
+        <v>328.375</v>
       </c>
       <c r="I657" t="n">
-        <v>240.6798714772972</v>
+        <v>354.7948621952361</v>
       </c>
       <c r="J657" t="n">
-        <v>410.7359879507638</v>
+        <v>410.8282292130136</v>
       </c>
       <c r="K657" t="n">
-        <v>411.4590087377502</v>
+        <v>411.55125</v>
       </c>
       <c r="L657" t="n">
-        <v>412.0915028588233</v>
+        <v>412.1837441210731</v>
       </c>
     </row>
     <row r="658">
@@ -26081,7 +26081,7 @@
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2021_2019_2018_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D658" t="n">
@@ -26096,22 +26096,22 @@
         <v>1.56</v>
       </c>
       <c r="G658" t="n">
-        <v>193.4845256701503</v>
+        <v>290.9970110990984</v>
       </c>
       <c r="H658" t="n">
-        <v>217.4875145710519</v>
+        <v>315</v>
       </c>
       <c r="I658" t="n">
-        <v>243.9073767662881</v>
+        <v>341.4198621952361</v>
       </c>
       <c r="J658" t="n">
-        <v>410.7479524335728</v>
+        <v>410.8011458796802</v>
       </c>
       <c r="K658" t="n">
-        <v>411.4709732205592</v>
+        <v>411.5241666666666</v>
       </c>
       <c r="L658" t="n">
-        <v>412.1034673416324</v>
+        <v>412.1566607877398</v>
       </c>
     </row>
     <row r="659">
@@ -26125,7 +26125,7 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2021_2019_2018_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D659" t="n">
@@ -26140,22 +26140,22 @@
         <v>1.33</v>
       </c>
       <c r="G659" t="n">
-        <v>200.5722518858103</v>
+        <v>279.5803444324317</v>
       </c>
       <c r="H659" t="n">
-        <v>224.5752407867119</v>
+        <v>303.5833333333333</v>
       </c>
       <c r="I659" t="n">
-        <v>250.995102981948</v>
+        <v>330.0031955285694</v>
       </c>
       <c r="J659" t="n">
-        <v>410.8173789392412</v>
+        <v>410.5473958796803</v>
       </c>
       <c r="K659" t="n">
-        <v>411.5403997262276</v>
+        <v>411.2704166666667</v>
       </c>
       <c r="L659" t="n">
-        <v>412.1728938473008</v>
+        <v>411.9029107877398</v>
       </c>
     </row>
     <row r="660">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2021_2019_2018_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D660" t="n">
@@ -26184,22 +26184,22 @@
         <v>0.97</v>
       </c>
       <c r="G660" t="n">
-        <v>199.7467655159695</v>
+        <v>274.9970110990984</v>
       </c>
       <c r="H660" t="n">
-        <v>223.7497544168711</v>
+        <v>299</v>
       </c>
       <c r="I660" t="n">
-        <v>250.1696166121072</v>
+        <v>325.4198621952361</v>
       </c>
       <c r="J660" t="n">
-        <v>410.8345676904888</v>
+        <v>410.285550641585</v>
       </c>
       <c r="K660" t="n">
-        <v>411.5575884774752</v>
+        <v>411.0085714285714</v>
       </c>
       <c r="L660" t="n">
-        <v>412.1900825985484</v>
+        <v>411.6410655496446</v>
       </c>
     </row>
     <row r="661">
@@ -26228,22 +26228,22 @@
         <v>3.23</v>
       </c>
       <c r="G661" t="n">
-        <v>206.1172289298858</v>
+        <v>280.0750738296755</v>
       </c>
       <c r="H661" t="n">
-        <v>230.1202178307874</v>
+        <v>304.0780627305771</v>
       </c>
       <c r="I661" t="n">
-        <v>256.5400800260236</v>
+        <v>330.4979249258133</v>
       </c>
       <c r="J661" t="n">
-        <v>410.8412022524927</v>
+        <v>410.8004071862192</v>
       </c>
       <c r="K661" t="n">
-        <v>411.5642230394791</v>
+        <v>411.5234279732056</v>
       </c>
       <c r="L661" t="n">
-        <v>412.1967171605522</v>
+        <v>412.1559220942787</v>
       </c>
     </row>
     <row r="662">
@@ -26272,22 +26272,22 @@
         <v>2</v>
       </c>
       <c r="G662" t="n">
-        <v>202.8081885513588</v>
+        <v>246.2243714062917</v>
       </c>
       <c r="H662" t="n">
-        <v>226.8111774522604</v>
+        <v>270.2273603071933</v>
       </c>
       <c r="I662" t="n">
-        <v>253.2310396474965</v>
+        <v>296.6472225024294</v>
       </c>
       <c r="J662" t="n">
-        <v>410.8454858154315</v>
+        <v>410.7955431731503</v>
       </c>
       <c r="K662" t="n">
-        <v>411.5685066024179</v>
+        <v>411.5185639601367</v>
       </c>
       <c r="L662" t="n">
-        <v>412.201000723491</v>
+        <v>412.1510580812098</v>
       </c>
     </row>
     <row r="663">
@@ -26316,22 +26316,22 @@
         <v>0.4</v>
       </c>
       <c r="G663" t="n">
-        <v>209.8290406905809</v>
+        <v>224.5772415403694</v>
       </c>
       <c r="H663" t="n">
-        <v>233.8320295914825</v>
+        <v>248.5802304412709</v>
       </c>
       <c r="I663" t="n">
-        <v>260.2518917867187</v>
+        <v>275.0000926365071</v>
       </c>
       <c r="J663" t="n">
-        <v>410.8452341934026</v>
+        <v>410.791150751388</v>
       </c>
       <c r="K663" t="n">
-        <v>411.568254980389</v>
+        <v>411.5141715383744</v>
       </c>
       <c r="L663" t="n">
-        <v>412.2007491014622</v>
+        <v>412.1466656594475</v>
       </c>
     </row>
     <row r="664">
@@ -26360,22 +26360,22 @@
         <v>1.05</v>
       </c>
       <c r="G664" t="n">
-        <v>207.1745221338405</v>
+        <v>192.4585366522892</v>
       </c>
       <c r="H664" t="n">
-        <v>231.1775110347421</v>
+        <v>216.4615255531908</v>
       </c>
       <c r="I664" t="n">
-        <v>257.5973732299782</v>
+        <v>242.8813877484269</v>
       </c>
       <c r="J664" t="n">
-        <v>410.8376845239449</v>
+        <v>410.7834270875034</v>
       </c>
       <c r="K664" t="n">
-        <v>411.5607053109313</v>
+        <v>411.5064478744898</v>
       </c>
       <c r="L664" t="n">
-        <v>412.1931994320044</v>
+        <v>412.1389419955629</v>
       </c>
     </row>
     <row r="665">
@@ -26404,22 +26404,22 @@
         <v>1.95</v>
       </c>
       <c r="G665" t="n">
-        <v>218.3131168741017</v>
+        <v>201.3513901635398</v>
       </c>
       <c r="H665" t="n">
-        <v>242.3161057750033</v>
+        <v>225.3543790644414</v>
       </c>
       <c r="I665" t="n">
-        <v>268.7359679702394</v>
+        <v>251.7742412596776</v>
       </c>
       <c r="J665" t="n">
-        <v>410.8027006862313</v>
+        <v>410.7476369902801</v>
       </c>
       <c r="K665" t="n">
-        <v>411.5257214732177</v>
+        <v>411.4706577772665</v>
       </c>
       <c r="L665" t="n">
-        <v>412.1582155942908</v>
+        <v>412.1031518983397</v>
       </c>
     </row>
     <row r="666">
@@ -26448,22 +26448,22 @@
         <v>2.29</v>
       </c>
       <c r="G666" t="n">
-        <v>225.3522913450871</v>
+        <v>206.3164981184654</v>
       </c>
       <c r="H666" t="n">
-        <v>249.3552802459887</v>
+        <v>230.319487019367</v>
       </c>
       <c r="I666" t="n">
-        <v>275.7751424412248</v>
+        <v>256.7393492146031</v>
       </c>
       <c r="J666" t="n">
-        <v>410.784305747746</v>
+        <v>410.728818110482</v>
       </c>
       <c r="K666" t="n">
-        <v>411.5073265347324</v>
+        <v>411.4518388974684</v>
       </c>
       <c r="L666" t="n">
-        <v>412.1398206558056</v>
+        <v>412.0843330185415</v>
       </c>
     </row>
     <row r="667">
@@ -26492,22 +26492,22 @@
         <v>0.53</v>
       </c>
       <c r="G667" t="n">
-        <v>230.3080916021526</v>
+        <v>209.2812082297963</v>
       </c>
       <c r="H667" t="n">
-        <v>254.3110805030542</v>
+        <v>233.2841971306979</v>
       </c>
       <c r="I667" t="n">
-        <v>280.7309426982903</v>
+        <v>259.7040593259341</v>
       </c>
       <c r="J667" t="n">
-        <v>410.7378492303779</v>
+        <v>410.6812909270187</v>
       </c>
       <c r="K667" t="n">
-        <v>411.4608700173643</v>
+        <v>411.4043117140051</v>
       </c>
       <c r="L667" t="n">
-        <v>412.0933641384374</v>
+        <v>412.0368058350783</v>
       </c>
     </row>
     <row r="668">
@@ -26536,22 +26536,22 @@
         <v>1.26</v>
       </c>
       <c r="G668" t="n">
-        <v>223.6489790024746</v>
+        <v>204.307864470827</v>
       </c>
       <c r="H668" t="n">
-        <v>247.6519679033761</v>
+        <v>228.3108533717286</v>
       </c>
       <c r="I668" t="n">
-        <v>274.0718300986123</v>
+        <v>254.7307155669648</v>
       </c>
       <c r="J668" t="n">
-        <v>410.6716464988473</v>
+        <v>410.6136641184689</v>
       </c>
       <c r="K668" t="n">
-        <v>411.3946672858337</v>
+        <v>411.3366849054553</v>
       </c>
       <c r="L668" t="n">
-        <v>412.0271614069069</v>
+        <v>411.9691790265284</v>
       </c>
     </row>
     <row r="669">
@@ -26580,22 +26580,22 @@
         <v>2.16</v>
       </c>
       <c r="G669" t="n">
-        <v>207.8702428200448</v>
+        <v>192.4166011538436</v>
       </c>
       <c r="H669" t="n">
-        <v>231.8732317209464</v>
+        <v>216.4195900547452</v>
       </c>
       <c r="I669" t="n">
-        <v>258.2930939161825</v>
+        <v>242.8394522499813</v>
       </c>
       <c r="J669" t="n">
-        <v>410.5942450716294</v>
+        <v>410.5347160244493</v>
       </c>
       <c r="K669" t="n">
-        <v>411.3172658586158</v>
+        <v>411.2577368114357</v>
       </c>
       <c r="L669" t="n">
-        <v>411.9497599796889</v>
+        <v>411.8902309325089</v>
       </c>
     </row>
     <row r="670">
@@ -26624,22 +26624,22 @@
         <v>2.97</v>
       </c>
       <c r="G670" t="n">
-        <v>208.2981882695101</v>
+        <v>195.6072224428119</v>
       </c>
       <c r="H670" t="n">
-        <v>232.3011771704117</v>
+        <v>219.6102113437135</v>
       </c>
       <c r="I670" t="n">
-        <v>258.7210393656479</v>
+        <v>246.0300735389497</v>
       </c>
       <c r="J670" t="n">
-        <v>410.5772811301519</v>
+        <v>410.5174389074641</v>
       </c>
       <c r="K670" t="n">
-        <v>411.3003019171383</v>
+        <v>411.2404596944505</v>
       </c>
       <c r="L670" t="n">
-        <v>411.9327960382114</v>
+        <v>411.8729538155236</v>
       </c>
     </row>
     <row r="671">
@@ -26671,19 +26671,19 @@
         <v>0</v>
       </c>
       <c r="H671" t="n">
-        <v>215.0296626134043</v>
+        <v>205.9965006562333</v>
       </c>
       <c r="I671" t="n">
-        <v>252.8583336051065</v>
+        <v>243.8251716479355</v>
       </c>
       <c r="J671" t="n">
-        <v>410.7227936186856</v>
+        <v>410.6624915833808</v>
       </c>
       <c r="K671" t="n">
-        <v>411.3085258604181</v>
+        <v>411.2482238251132</v>
       </c>
       <c r="L671" t="n">
-        <v>411.5889858560625</v>
+        <v>411.5286838207577</v>
       </c>
     </row>
     <row r="672">
@@ -26715,19 +26715,19 @@
         <v>0</v>
       </c>
       <c r="H672" t="n">
-        <v>219.2289046263132</v>
+        <v>212.9300407770615</v>
       </c>
       <c r="I672" t="n">
-        <v>257.0575756180153</v>
+        <v>250.7587117687637</v>
       </c>
       <c r="J672" t="n">
-        <v>410.7135032587876</v>
+        <v>410.6530577750467</v>
       </c>
       <c r="K672" t="n">
-        <v>411.29923550052</v>
+        <v>411.2387900167791</v>
       </c>
       <c r="L672" t="n">
-        <v>411.5796954961645</v>
+        <v>411.5192500124236</v>
       </c>
     </row>
     <row r="673">
@@ -26759,19 +26759,19 @@
         <v>0</v>
       </c>
       <c r="H673" t="n">
-        <v>204.4727429222506</v>
+        <v>201.4571272315475</v>
       </c>
       <c r="I673" t="n">
-        <v>242.3014139139527</v>
+        <v>239.2857982232496</v>
       </c>
       <c r="J673" t="n">
-        <v>410.7271519929035</v>
+        <v>410.6660657289702</v>
       </c>
       <c r="K673" t="n">
-        <v>411.3128842346359</v>
+        <v>411.2517979707026</v>
       </c>
       <c r="L673" t="n">
-        <v>411.5933442302804</v>
+        <v>411.5322579663471</v>
       </c>
     </row>
     <row r="674">
@@ -26806,16 +26806,16 @@
         <v>185.2624182360328</v>
       </c>
       <c r="I674" t="n">
-        <v>223.091089227735</v>
+        <v>223.0910892277349</v>
       </c>
       <c r="J674" t="n">
-        <v>410.782088917481</v>
+        <v>410.7186756221379</v>
       </c>
       <c r="K674" t="n">
-        <v>411.3678211592135</v>
+        <v>411.3044078638704</v>
       </c>
       <c r="L674" t="n">
-        <v>411.648281154858</v>
+        <v>411.5848678595149</v>
       </c>
     </row>
     <row r="675">
@@ -26853,13 +26853,13 @@
         <v>230.9579549645171</v>
       </c>
       <c r="J675" t="n">
-        <v>410.8363753270768</v>
+        <v>410.7706625549935</v>
       </c>
       <c r="K675" t="n">
-        <v>411.4221075688092</v>
+        <v>411.3563947967259</v>
       </c>
       <c r="L675" t="n">
-        <v>411.7025675644537</v>
+        <v>411.6368547923704</v>
       </c>
     </row>
     <row r="676">
@@ -26891,19 +26891,19 @@
         <v>0</v>
       </c>
       <c r="H676" t="n">
-        <v>188.7018288533136</v>
+        <v>188.7018288533135</v>
       </c>
       <c r="I676" t="n">
-        <v>226.5304998450158</v>
+        <v>226.5304998450157</v>
       </c>
       <c r="J676" t="n">
-        <v>410.8566494807022</v>
+        <v>410.7900779311636</v>
       </c>
       <c r="K676" t="n">
-        <v>411.4423817224347</v>
+        <v>411.375810172896</v>
       </c>
       <c r="L676" t="n">
-        <v>411.7228417180792</v>
+        <v>411.6562701685405</v>
       </c>
     </row>
     <row r="677">
@@ -26938,16 +26938,16 @@
         <v>177.808778371837</v>
       </c>
       <c r="I677" t="n">
-        <v>215.6374493635392</v>
+        <v>215.6374493635391</v>
       </c>
       <c r="J677" t="n">
-        <v>410.8743470417038</v>
+        <v>410.8070258546372</v>
       </c>
       <c r="K677" t="n">
-        <v>411.4600792834362</v>
+        <v>411.3927580963697</v>
       </c>
       <c r="L677" t="n">
-        <v>411.7405392790807</v>
+        <v>411.6732180920142</v>
       </c>
     </row>
     <row r="678">
@@ -26982,16 +26982,16 @@
         <v>187.5467951592674</v>
       </c>
       <c r="I678" t="n">
-        <v>225.3754661509696</v>
+        <v>225.3754661509695</v>
       </c>
       <c r="J678" t="n">
-        <v>410.9113406245126</v>
+        <v>410.8424524544048</v>
       </c>
       <c r="K678" t="n">
-        <v>411.497072866245</v>
+        <v>411.4281846961372</v>
       </c>
       <c r="L678" t="n">
-        <v>411.7775328618895</v>
+        <v>411.7086446917817</v>
       </c>
     </row>
     <row r="679">
@@ -27029,13 +27029,13 @@
         <v>249.5197903067904</v>
       </c>
       <c r="J679" t="n">
-        <v>410.9258227468732</v>
+        <v>410.8563211395576</v>
       </c>
       <c r="K679" t="n">
-        <v>411.5115549886057</v>
+        <v>411.4420533812901</v>
       </c>
       <c r="L679" t="n">
-        <v>411.7920149842502</v>
+        <v>411.7225133769346</v>
       </c>
     </row>
     <row r="680">
@@ -27067,19 +27067,19 @@
         <v>0</v>
       </c>
       <c r="H680" t="n">
-        <v>221.010913597745</v>
+        <v>221.0109135977449</v>
       </c>
       <c r="I680" t="n">
-        <v>258.8395845894472</v>
+        <v>258.8395845894471</v>
       </c>
       <c r="J680" t="n">
-        <v>410.9182369099814</v>
+        <v>410.8486408710951</v>
       </c>
       <c r="K680" t="n">
-        <v>411.5039691517139</v>
+        <v>411.4343731128275</v>
       </c>
       <c r="L680" t="n">
-        <v>411.7844291473584</v>
+        <v>411.714833108472</v>
       </c>
     </row>
     <row r="681">
@@ -27111,19 +27111,19 @@
         <v>0</v>
       </c>
       <c r="H681" t="n">
-        <v>233.3426846089203</v>
+        <v>233.3426846089202</v>
       </c>
       <c r="I681" t="n">
-        <v>271.1713556006225</v>
+        <v>271.1713556006224</v>
       </c>
       <c r="J681" t="n">
-        <v>410.9238216765808</v>
+        <v>410.8539890768133</v>
       </c>
       <c r="K681" t="n">
-        <v>411.5095539183133</v>
+        <v>411.4397213185457</v>
       </c>
       <c r="L681" t="n">
-        <v>411.7900139139578</v>
+        <v>411.7201813141902</v>
       </c>
     </row>
     <row r="682">
@@ -27155,19 +27155,19 @@
         <v>0</v>
       </c>
       <c r="H682" t="n">
-        <v>261.3015731745737</v>
+        <v>261.3015731745735</v>
       </c>
       <c r="I682" t="n">
-        <v>299.1302441662758</v>
+        <v>299.1302441662757</v>
       </c>
       <c r="J682" t="n">
-        <v>410.9640787877939</v>
+        <v>410.8925409676672</v>
       </c>
       <c r="K682" t="n">
-        <v>411.5498110295264</v>
+        <v>411.4782732093997</v>
       </c>
       <c r="L682" t="n">
-        <v>411.8302710251709</v>
+        <v>411.7587332050442</v>
       </c>
     </row>
     <row r="683">
@@ -27199,19 +27199,19 @@
         <v>0</v>
       </c>
       <c r="H683" t="n">
-        <v>288.6302383059395</v>
+        <v>288.6302383059394</v>
       </c>
       <c r="I683" t="n">
         <v>326.4589092976416</v>
       </c>
       <c r="J683" t="n">
-        <v>410.9610016035148</v>
+        <v>410.8894254773516</v>
       </c>
       <c r="K683" t="n">
-        <v>411.5467338452472</v>
+        <v>411.475157719084</v>
       </c>
       <c r="L683" t="n">
-        <v>411.8271938408917</v>
+        <v>411.7556177147285</v>
       </c>
     </row>
     <row r="684">
@@ -27243,19 +27243,19 @@
         <v>0</v>
       </c>
       <c r="H684" t="n">
-        <v>305.0374003261422</v>
+        <v>305.0374003261421</v>
       </c>
       <c r="I684" t="n">
-        <v>342.8660713178443</v>
+        <v>342.8660713178442</v>
       </c>
       <c r="J684" t="n">
-        <v>410.9498165405032</v>
+        <v>410.8781011781446</v>
       </c>
       <c r="K684" t="n">
-        <v>411.5355487822357</v>
+        <v>411.463833419877</v>
       </c>
       <c r="L684" t="n">
-        <v>411.8160087778801</v>
+        <v>411.7442934155215</v>
       </c>
     </row>
     <row r="685">
@@ -27287,19 +27287,19 @@
         <v>0</v>
       </c>
       <c r="H685" t="n">
-        <v>317.780216664089</v>
+        <v>317.7802166640889</v>
       </c>
       <c r="I685" t="n">
-        <v>355.6088876557911</v>
+        <v>355.608887655791</v>
       </c>
       <c r="J685" t="n">
-        <v>410.9496200836918</v>
+        <v>410.877902275759</v>
       </c>
       <c r="K685" t="n">
-        <v>411.5353523254242</v>
+        <v>411.4636345174914</v>
       </c>
       <c r="L685" t="n">
-        <v>411.8158123210687</v>
+        <v>411.7440945131359</v>
       </c>
     </row>
     <row r="686">
@@ -27334,16 +27334,16 @@
         <v>320.106988937391</v>
       </c>
       <c r="I686" t="n">
-        <v>357.9356599290932</v>
+        <v>357.9356599290931</v>
       </c>
       <c r="J686" t="n">
-        <v>410.9377194871615</v>
+        <v>410.8658535357822</v>
       </c>
       <c r="K686" t="n">
-        <v>411.523451728894</v>
+        <v>411.4515857775147</v>
       </c>
       <c r="L686" t="n">
-        <v>411.8039117245385</v>
+        <v>411.7320457731591</v>
       </c>
     </row>
     <row r="687">
@@ -27375,19 +27375,19 @@
         <v>0</v>
       </c>
       <c r="H687" t="n">
-        <v>313.6701013827312</v>
+        <v>313.6701013827311</v>
       </c>
       <c r="I687" t="n">
-        <v>351.4987723744334</v>
+        <v>351.4987723744333</v>
       </c>
       <c r="J687" t="n">
-        <v>410.934856394435</v>
+        <v>410.8629548021175</v>
       </c>
       <c r="K687" t="n">
-        <v>411.5205886361674</v>
+        <v>411.44868704385</v>
       </c>
       <c r="L687" t="n">
-        <v>411.8010486318119</v>
+        <v>411.7291470394945</v>
       </c>
     </row>
     <row r="688">
@@ -27422,16 +27422,16 @@
         <v>301.5033118860746</v>
       </c>
       <c r="I688" t="n">
-        <v>339.3319828777768</v>
+        <v>339.3319828777767</v>
       </c>
       <c r="J688" t="n">
-        <v>410.944937732776</v>
+        <v>410.8726091127145</v>
       </c>
       <c r="K688" t="n">
-        <v>411.5306699745084</v>
+        <v>411.4583413544469</v>
       </c>
       <c r="L688" t="n">
-        <v>411.8111299701529</v>
+        <v>411.7388013500914</v>
       </c>
     </row>
     <row r="689">
@@ -27466,16 +27466,16 @@
         <v>299.7458178038003</v>
       </c>
       <c r="I689" t="n">
-        <v>337.5744887955025</v>
+        <v>337.5744887955024</v>
       </c>
       <c r="J689" t="n">
-        <v>410.970281498012</v>
+        <v>410.8968793606722</v>
       </c>
       <c r="K689" t="n">
-        <v>411.5560137397445</v>
+        <v>411.4826116024046</v>
       </c>
       <c r="L689" t="n">
-        <v>411.8364737353889</v>
+        <v>411.7630715980491</v>
       </c>
     </row>
     <row r="690">
@@ -27507,19 +27507,19 @@
         <v>0</v>
       </c>
       <c r="H690" t="n">
-        <v>285.9855591495999</v>
+        <v>285.9855591495997</v>
       </c>
       <c r="I690" t="n">
-        <v>323.814230141302</v>
+        <v>323.8142301413019</v>
       </c>
       <c r="J690" t="n">
-        <v>410.9934814103542</v>
+        <v>410.9190965655705</v>
       </c>
       <c r="K690" t="n">
-        <v>411.5792136520867</v>
+        <v>411.5048288073029</v>
       </c>
       <c r="L690" t="n">
-        <v>411.8596736477311</v>
+        <v>411.7852888029474</v>
       </c>
     </row>
     <row r="691">
@@ -27554,16 +27554,16 @@
         <v>274.3316114544743</v>
       </c>
       <c r="I691" t="n">
-        <v>312.1602824461765</v>
+        <v>312.1602824461764</v>
       </c>
       <c r="J691" t="n">
-        <v>411.0078887150596</v>
+        <v>410.9328936022123</v>
       </c>
       <c r="K691" t="n">
-        <v>411.593620956792</v>
+        <v>411.5186258439447</v>
       </c>
       <c r="L691" t="n">
-        <v>411.8740809524365</v>
+        <v>411.7990858395892</v>
       </c>
     </row>
     <row r="692">
@@ -27595,19 +27595,19 @@
         <v>0</v>
       </c>
       <c r="H692" t="n">
-        <v>255.8001361422271</v>
+        <v>255.800136142227</v>
       </c>
       <c r="I692" t="n">
         <v>293.6288071339292</v>
       </c>
       <c r="J692" t="n">
-        <v>411.005276922966</v>
+        <v>410.9302492974729</v>
       </c>
       <c r="K692" t="n">
-        <v>411.5910091646984</v>
+        <v>411.5159815392053</v>
       </c>
       <c r="L692" t="n">
-        <v>411.8714691603429</v>
+        <v>411.7964415348498</v>
       </c>
     </row>
     <row r="693">
@@ -27639,19 +27639,19 @@
         <v>0</v>
       </c>
       <c r="H693" t="n">
-        <v>240.7495988270116</v>
+        <v>240.7495988270115</v>
       </c>
       <c r="I693" t="n">
-        <v>278.5782698187137</v>
+        <v>278.5782698187136</v>
       </c>
       <c r="J693" t="n">
-        <v>410.9886554549865</v>
+        <v>410.9134209187265</v>
       </c>
       <c r="K693" t="n">
-        <v>411.5743876967189</v>
+        <v>411.4991531604589</v>
       </c>
       <c r="L693" t="n">
-        <v>411.8548476923634</v>
+        <v>411.7796131561034</v>
       </c>
     </row>
     <row r="694">
@@ -27683,19 +27683,19 @@
         <v>0</v>
       </c>
       <c r="H694" t="n">
-        <v>221.4306268756659</v>
+        <v>221.4306268756658</v>
       </c>
       <c r="I694" t="n">
         <v>259.259297867368</v>
       </c>
       <c r="J694" t="n">
-        <v>410.9021443425401</v>
+        <v>410.8258328809063</v>
       </c>
       <c r="K694" t="n">
-        <v>411.4878765842725</v>
+        <v>411.4115651226388</v>
       </c>
       <c r="L694" t="n">
-        <v>411.768336579917</v>
+        <v>411.6920251182833</v>
       </c>
     </row>
     <row r="695">
@@ -27730,16 +27730,16 @@
         <v>201.97954333465</v>
       </c>
       <c r="I695" t="n">
-        <v>239.8082143263522</v>
+        <v>239.8082143263521</v>
       </c>
       <c r="J695" t="n">
-        <v>410.8681826403982</v>
+        <v>410.7914484097382</v>
       </c>
       <c r="K695" t="n">
-        <v>411.4539148821307</v>
+        <v>411.3771806514707</v>
       </c>
       <c r="L695" t="n">
-        <v>411.7343748777752</v>
+        <v>411.6576406471152</v>
       </c>
     </row>
     <row r="696">
@@ -27777,13 +27777,13 @@
         <v>223.6196450453489</v>
       </c>
       <c r="J696" t="n">
-        <v>410.8261523419686</v>
+        <v>410.7488949011271</v>
       </c>
       <c r="K696" t="n">
-        <v>411.411884583701</v>
+        <v>411.3346271428595</v>
       </c>
       <c r="L696" t="n">
-        <v>411.6923445793455</v>
+        <v>411.615087138504</v>
       </c>
     </row>
     <row r="697">
@@ -27821,13 +27821,13 @@
         <v>225.2439331646677</v>
       </c>
       <c r="J697" t="n">
-        <v>410.7913508382341</v>
+        <v>410.7136601741759</v>
       </c>
       <c r="K697" t="n">
-        <v>411.3770830799666</v>
+        <v>411.2993924159083</v>
       </c>
       <c r="L697" t="n">
-        <v>411.657543075611</v>
+        <v>411.5798524115528</v>
       </c>
     </row>
     <row r="698">
@@ -27862,16 +27862,16 @@
         <v>227.1330640655555</v>
       </c>
       <c r="I698" t="n">
-        <v>264.9617350572577</v>
+        <v>264.9617350572576</v>
       </c>
       <c r="J698" t="n">
-        <v>410.7866596983778</v>
+        <v>410.7089092938928</v>
       </c>
       <c r="K698" t="n">
-        <v>411.3723919401102</v>
+        <v>411.2946415356253</v>
       </c>
       <c r="L698" t="n">
-        <v>411.6528519357547</v>
+        <v>411.5751015312698</v>
       </c>
     </row>
     <row r="699">
@@ -27906,16 +27906,16 @@
         <v>250.0014312142591</v>
       </c>
       <c r="I699" t="n">
-        <v>287.8301022059613</v>
+        <v>287.8301022059612</v>
       </c>
       <c r="J699" t="n">
-        <v>410.829119477688</v>
+        <v>410.7495175173069</v>
       </c>
       <c r="K699" t="n">
-        <v>411.4148517194205</v>
+        <v>411.3352497590394</v>
       </c>
       <c r="L699" t="n">
-        <v>411.695311715065</v>
+        <v>411.6157097546838</v>
       </c>
     </row>
     <row r="700">
@@ -27953,13 +27953,13 @@
         <v>318.9083568930857</v>
       </c>
       <c r="J700" t="n">
-        <v>410.8004342218217</v>
+        <v>410.7204504449412</v>
       </c>
       <c r="K700" t="n">
-        <v>411.3861664635542</v>
+        <v>411.3061826866736</v>
       </c>
       <c r="L700" t="n">
-        <v>411.6666264591987</v>
+        <v>411.5866426823181</v>
       </c>
     </row>
     <row r="701">
@@ -27991,19 +27991,19 @@
         <v>150.4184080007088</v>
       </c>
       <c r="H701" t="n">
-        <v>205.1026612409571</v>
+        <v>205.102661240957</v>
       </c>
       <c r="I701" t="n">
         <v>219.6724822090281</v>
       </c>
       <c r="J701" t="n">
-        <v>410.5227687299331</v>
+        <v>410.4426938880873</v>
       </c>
       <c r="K701" t="n">
-        <v>411.3881979812763</v>
+        <v>411.3081231394304</v>
       </c>
       <c r="L701" t="n">
-        <v>411.5394812415592</v>
+        <v>411.4594063997133</v>
       </c>
     </row>
     <row r="702">
@@ -28032,22 +28032,22 @@
         <v>0.19</v>
       </c>
       <c r="G702" t="n">
-        <v>223.4290199819132</v>
+        <v>223.4290199819131</v>
       </c>
       <c r="H702" t="n">
-        <v>278.1132732221615</v>
+        <v>278.1132732221614</v>
       </c>
       <c r="I702" t="n">
-        <v>292.6830941902325</v>
+        <v>292.6830941902324</v>
       </c>
       <c r="J702" t="n">
-        <v>410.5150076793777</v>
+        <v>410.434825031862</v>
       </c>
       <c r="K702" t="n">
-        <v>411.3804369307209</v>
+        <v>411.3002542832052</v>
       </c>
       <c r="L702" t="n">
-        <v>411.5317201910038</v>
+        <v>411.451537543488</v>
       </c>
     </row>
     <row r="703">
@@ -28079,19 +28079,19 @@
         <v>267.0843217261476</v>
       </c>
       <c r="H703" t="n">
-        <v>321.7685749663959</v>
+        <v>321.7685749663958</v>
       </c>
       <c r="I703" t="n">
         <v>336.3383959344669</v>
       </c>
       <c r="J703" t="n">
-        <v>410.4840045844333</v>
+        <v>410.4033822437502</v>
       </c>
       <c r="K703" t="n">
-        <v>411.3494338357765</v>
+        <v>411.2688114950934</v>
       </c>
       <c r="L703" t="n">
-        <v>411.5007170960594</v>
+        <v>411.4200947553762</v>
       </c>
     </row>
     <row r="704">
@@ -28120,22 +28120,22 @@
         <v>0.24</v>
       </c>
       <c r="G704" t="n">
-        <v>319.2763347100123</v>
+        <v>319.2763347100122</v>
       </c>
       <c r="H704" t="n">
-        <v>373.9605879502606</v>
+        <v>373.9605879502605</v>
       </c>
       <c r="I704" t="n">
-        <v>388.5304089183316</v>
+        <v>388.5304089183315</v>
       </c>
       <c r="J704" t="n">
-        <v>410.4310280793685</v>
+        <v>410.3496389067167</v>
       </c>
       <c r="K704" t="n">
-        <v>411.2964573307117</v>
+        <v>411.2150681580599</v>
       </c>
       <c r="L704" t="n">
-        <v>411.4477405909946</v>
+        <v>411.3663514183428</v>
       </c>
     </row>
     <row r="705">
@@ -28164,22 +28164,22 @@
         <v>0</v>
       </c>
       <c r="G705" t="n">
-        <v>312.5173267148292</v>
+        <v>312.5173267148291</v>
       </c>
       <c r="H705" t="n">
         <v>367.2015799550774</v>
       </c>
       <c r="I705" t="n">
-        <v>381.7714009231485</v>
+        <v>381.7714009231484</v>
       </c>
       <c r="J705" t="n">
-        <v>410.4316879326622</v>
+        <v>410.3502680109336</v>
       </c>
       <c r="K705" t="n">
-        <v>411.2971171840054</v>
+        <v>411.2156972622768</v>
       </c>
       <c r="L705" t="n">
-        <v>411.4484004442883</v>
+        <v>411.3669805225596</v>
       </c>
     </row>
     <row r="706">
@@ -28217,13 +28217,13 @@
         <v>345.9711529002387</v>
       </c>
       <c r="J706" t="n">
-        <v>410.4179834003684</v>
+        <v>410.3363651062959</v>
       </c>
       <c r="K706" t="n">
-        <v>411.2834126517116</v>
+        <v>411.2017943576391</v>
       </c>
       <c r="L706" t="n">
-        <v>411.4346959119945</v>
+        <v>411.3530776179219</v>
       </c>
     </row>
     <row r="707">
@@ -28252,22 +28252,22 @@
         <v>0</v>
       </c>
       <c r="G707" t="n">
-        <v>236.6918172281116</v>
+        <v>236.6918172281115</v>
       </c>
       <c r="H707" t="n">
         <v>291.3760704683598</v>
       </c>
       <c r="I707" t="n">
-        <v>305.9458914364309</v>
+        <v>305.9458914364308</v>
       </c>
       <c r="J707" t="n">
-        <v>410.4200733446297</v>
+        <v>410.3383576594288</v>
       </c>
       <c r="K707" t="n">
-        <v>411.2855025959728</v>
+        <v>411.203786910772</v>
       </c>
       <c r="L707" t="n">
-        <v>411.4367858562557</v>
+        <v>411.3550701710549</v>
       </c>
     </row>
     <row r="708">
@@ -28296,22 +28296,22 @@
         <v>0</v>
       </c>
       <c r="G708" t="n">
-        <v>223.8867189187417</v>
+        <v>223.8867189187416</v>
       </c>
       <c r="H708" t="n">
         <v>278.5709721589899</v>
       </c>
       <c r="I708" t="n">
-        <v>293.140793127061</v>
+        <v>293.1407931270609</v>
       </c>
       <c r="J708" t="n">
-        <v>410.4199387784584</v>
+        <v>410.3382211454197</v>
       </c>
       <c r="K708" t="n">
-        <v>411.2853680298016</v>
+        <v>411.2036503967629</v>
       </c>
       <c r="L708" t="n">
-        <v>411.4366512900845</v>
+        <v>411.3549336570458</v>
       </c>
     </row>
     <row r="709">
@@ -28340,22 +28340,22 @@
         <v>0</v>
       </c>
       <c r="G709" t="n">
-        <v>208.9908478184492</v>
+        <v>208.9908478184491</v>
       </c>
       <c r="H709" t="n">
-        <v>263.6751010586975</v>
+        <v>263.6751010586974</v>
       </c>
       <c r="I709" t="n">
-        <v>278.2449220267685</v>
+        <v>278.2449220267684</v>
       </c>
       <c r="J709" t="n">
-        <v>410.4605919769146</v>
+        <v>410.3769799101657</v>
       </c>
       <c r="K709" t="n">
-        <v>411.3260212282578</v>
+        <v>411.2424091615089</v>
       </c>
       <c r="L709" t="n">
-        <v>411.4773044885407</v>
+        <v>411.3936924217918</v>
       </c>
     </row>
     <row r="710">
@@ -28384,22 +28384,22 @@
         <v>0</v>
       </c>
       <c r="G710" t="n">
-        <v>183.8570108670272</v>
+        <v>183.8570108670271</v>
       </c>
       <c r="H710" t="n">
-        <v>238.5412641072755</v>
+        <v>238.5412641072754</v>
       </c>
       <c r="I710" t="n">
-        <v>253.1110850753465</v>
+        <v>253.1110850753464</v>
       </c>
       <c r="J710" t="n">
-        <v>410.4637751353688</v>
+        <v>410.380014733854</v>
       </c>
       <c r="K710" t="n">
-        <v>411.329204386712</v>
+        <v>411.2454439851972</v>
       </c>
       <c r="L710" t="n">
-        <v>411.4804876469949</v>
+        <v>411.3967272454801</v>
       </c>
     </row>
     <row r="711">
@@ -28437,13 +28437,13 @@
         <v>240.1784925743821</v>
       </c>
       <c r="J711" t="n">
-        <v>410.4838061497571</v>
+        <v>410.3991123056018</v>
       </c>
       <c r="K711" t="n">
-        <v>411.3492354011003</v>
+        <v>411.264541556945</v>
       </c>
       <c r="L711" t="n">
-        <v>411.5005186613832</v>
+        <v>411.4158248172279</v>
       </c>
     </row>
     <row r="712">
@@ -28475,19 +28475,19 @@
         <v>156.0630867213704</v>
       </c>
       <c r="H712" t="n">
-        <v>210.7473399616187</v>
+        <v>210.7473399616186</v>
       </c>
       <c r="I712" t="n">
         <v>225.3171609296897</v>
       </c>
       <c r="J712" t="n">
-        <v>410.4765928395355</v>
+        <v>410.3917945831153</v>
       </c>
       <c r="K712" t="n">
-        <v>411.3420220908787</v>
+        <v>411.2572238344585</v>
       </c>
       <c r="L712" t="n">
-        <v>411.4933053511616</v>
+        <v>411.4085070947414</v>
       </c>
     </row>
     <row r="713">
@@ -28522,16 +28522,16 @@
         <v>197.6487212683919</v>
       </c>
       <c r="I713" t="n">
-        <v>212.218542236463</v>
+        <v>212.2185422364629</v>
       </c>
       <c r="J713" t="n">
-        <v>410.4900430962491</v>
+        <v>410.404618059632</v>
       </c>
       <c r="K713" t="n">
-        <v>411.3554723475922</v>
+        <v>411.2700473109751</v>
       </c>
       <c r="L713" t="n">
-        <v>411.5067556078751</v>
+        <v>411.4213305712581</v>
       </c>
     </row>
     <row r="714">
@@ -28563,19 +28563,19 @@
         <v>136.7192998319365</v>
       </c>
       <c r="H714" t="n">
-        <v>191.4035530721848</v>
+        <v>191.4035530721847</v>
       </c>
       <c r="I714" t="n">
         <v>205.9733740402558</v>
       </c>
       <c r="J714" t="n">
-        <v>410.4853559060368</v>
+        <v>410.3998630226017</v>
       </c>
       <c r="K714" t="n">
-        <v>411.35078515738</v>
+        <v>411.2652922739449</v>
       </c>
       <c r="L714" t="n">
-        <v>411.5020684176628</v>
+        <v>411.4165755342277</v>
       </c>
     </row>
     <row r="715">
@@ -28607,19 +28607,19 @@
         <v>133.3980686644564</v>
       </c>
       <c r="H715" t="n">
-        <v>188.0823219047047</v>
+        <v>188.0823219047046</v>
       </c>
       <c r="I715" t="n">
         <v>202.6521428727757</v>
       </c>
       <c r="J715" t="n">
-        <v>410.4604704523737</v>
+        <v>410.3746173533789</v>
       </c>
       <c r="K715" t="n">
-        <v>411.3258997037169</v>
+        <v>411.2400466047221</v>
       </c>
       <c r="L715" t="n">
-        <v>411.4771829639998</v>
+        <v>411.391329865005</v>
       </c>
     </row>
     <row r="716">
@@ -28651,19 +28651,19 @@
         <v>127.1980991834929</v>
       </c>
       <c r="H716" t="n">
-        <v>181.8823524237412</v>
+        <v>181.8823524237411</v>
       </c>
       <c r="I716" t="n">
         <v>196.4521733918122</v>
       </c>
       <c r="J716" t="n">
-        <v>410.4570920359276</v>
+        <v>410.3711900345424</v>
       </c>
       <c r="K716" t="n">
-        <v>411.3225212872708</v>
+        <v>411.2366192858856</v>
       </c>
       <c r="L716" t="n">
-        <v>411.4738045475536</v>
+        <v>411.3879025461684</v>
       </c>
     </row>
     <row r="717">
@@ -28692,7 +28692,7 @@
         <v>0</v>
       </c>
       <c r="G717" t="n">
-        <v>132.0879621960625</v>
+        <v>132.0879621960624</v>
       </c>
       <c r="H717" t="n">
         <v>186.7722154363107</v>
@@ -28701,13 +28701,13 @@
         <v>201.3420364043818</v>
       </c>
       <c r="J717" t="n">
-        <v>410.4631861424663</v>
+        <v>410.3770001565165</v>
       </c>
       <c r="K717" t="n">
-        <v>411.3286153938095</v>
+        <v>411.2424294078597</v>
       </c>
       <c r="L717" t="n">
-        <v>411.4798986540924</v>
+        <v>411.3937126681426</v>
       </c>
     </row>
     <row r="718">
@@ -28736,22 +28736,22 @@
         <v>0.02</v>
       </c>
       <c r="G718" t="n">
-        <v>132.427513087011</v>
+        <v>132.4275130870109</v>
       </c>
       <c r="H718" t="n">
         <v>187.1117663272592</v>
       </c>
       <c r="I718" t="n">
-        <v>201.6815872953303</v>
+        <v>201.6815872953302</v>
       </c>
       <c r="J718" t="n">
-        <v>410.460504547247</v>
+        <v>410.3742797453554</v>
       </c>
       <c r="K718" t="n">
-        <v>411.3259337985902</v>
+        <v>411.2397089966986</v>
       </c>
       <c r="L718" t="n">
-        <v>411.4772170588731</v>
+        <v>411.3909922569815</v>
       </c>
     </row>
     <row r="719">
@@ -28783,19 +28783,19 @@
         <v>130.716652172868</v>
       </c>
       <c r="H719" t="n">
-        <v>185.4009054131163</v>
+        <v>185.4009054131162</v>
       </c>
       <c r="I719" t="n">
         <v>199.9707263811873</v>
       </c>
       <c r="J719" t="n">
-        <v>410.4177799419472</v>
+        <v>410.3309367037666</v>
       </c>
       <c r="K719" t="n">
-        <v>411.2832091932904</v>
+        <v>411.1963659551097</v>
       </c>
       <c r="L719" t="n">
-        <v>411.4344924535733</v>
+        <v>411.3476492153926</v>
       </c>
     </row>
     <row r="720">
@@ -28833,13 +28833,13 @@
         <v>196.5859218896878</v>
       </c>
       <c r="J720" t="n">
-        <v>410.4365652303906</v>
+        <v>410.3488466002349</v>
       </c>
       <c r="K720" t="n">
-        <v>411.3019944817338</v>
+        <v>411.2142758515781</v>
       </c>
       <c r="L720" t="n">
-        <v>411.4532777420167</v>
+        <v>411.365559111861</v>
       </c>
     </row>
     <row r="721">
@@ -28877,13 +28877,13 @@
         <v>194.4413169663419</v>
       </c>
       <c r="J721" t="n">
-        <v>410.4354412485077</v>
+        <v>410.3477063487766</v>
       </c>
       <c r="K721" t="n">
-        <v>411.3008704998509</v>
+        <v>411.2131356001198</v>
       </c>
       <c r="L721" t="n">
-        <v>411.4521537601338</v>
+        <v>411.3644188604027</v>
       </c>
     </row>
     <row r="722">
@@ -28921,13 +28921,13 @@
         <v>190.9381651414691</v>
       </c>
       <c r="J722" t="n">
-        <v>410.4070949747764</v>
+        <v>410.3189497643074</v>
       </c>
       <c r="K722" t="n">
-        <v>411.2725242261196</v>
+        <v>411.1843790156506</v>
       </c>
       <c r="L722" t="n">
-        <v>411.4238074864024</v>
+        <v>411.3356622759335</v>
       </c>
     </row>
     <row r="723">
@@ -28965,13 +28965,13 @@
         <v>187.7293684064092</v>
       </c>
       <c r="J723" t="n">
-        <v>410.3948704502711</v>
+        <v>410.3065482904888</v>
       </c>
       <c r="K723" t="n">
-        <v>411.2602997016143</v>
+        <v>411.171977541832</v>
       </c>
       <c r="L723" t="n">
-        <v>411.4115829618972</v>
+        <v>411.3232608021149</v>
       </c>
     </row>
     <row r="724">
@@ -29003,19 +29003,19 @@
         <v>121.6118916528941</v>
       </c>
       <c r="H724" t="n">
-        <v>176.2961448931424</v>
+        <v>176.2961448931423</v>
       </c>
       <c r="I724" t="n">
         <v>190.8659658612134</v>
       </c>
       <c r="J724" t="n">
-        <v>410.3822533640663</v>
+        <v>410.293748572662</v>
       </c>
       <c r="K724" t="n">
-        <v>411.2476826154095</v>
+        <v>411.1591778240052</v>
       </c>
       <c r="L724" t="n">
-        <v>411.3989658756924</v>
+        <v>411.310461084288</v>
       </c>
     </row>
     <row r="725">
@@ -29044,22 +29044,22 @@
         <v>0</v>
       </c>
       <c r="G725" t="n">
-        <v>112.9155052685871</v>
+        <v>112.915505268587</v>
       </c>
       <c r="H725" t="n">
         <v>167.5997585088353</v>
       </c>
       <c r="I725" t="n">
-        <v>182.1695794769064</v>
+        <v>182.1695794769063</v>
       </c>
       <c r="J725" t="n">
-        <v>410.2494287176726</v>
+        <v>410.1590012968881</v>
       </c>
       <c r="K725" t="n">
-        <v>411.1148579690158</v>
+        <v>411.0244305482313</v>
       </c>
       <c r="L725" t="n">
-        <v>411.2661412292987</v>
+        <v>411.1757138085142</v>
       </c>
     </row>
     <row r="726">
@@ -29097,13 +29097,13 @@
         <v>168.6331261211036</v>
       </c>
       <c r="J726" t="n">
-        <v>410.1135200789781</v>
+        <v>410.0211253881961</v>
       </c>
       <c r="K726" t="n">
-        <v>410.9789493303213</v>
+        <v>410.8865546395393</v>
       </c>
       <c r="L726" t="n">
-        <v>411.1302325906041</v>
+        <v>411.0378378998222</v>
       </c>
     </row>
     <row r="727">
@@ -29141,13 +29141,13 @@
         <v>173.5011462402723</v>
       </c>
       <c r="J727" t="n">
-        <v>410.0619119054255</v>
+        <v>409.9687701891974</v>
       </c>
       <c r="K727" t="n">
-        <v>410.9273411567687</v>
+        <v>410.8341994405406</v>
       </c>
       <c r="L727" t="n">
-        <v>411.0786244170516</v>
+        <v>410.9854827008235</v>
       </c>
     </row>
     <row r="728">
@@ -29185,13 +29185,13 @@
         <v>171.3463148643339</v>
       </c>
       <c r="J728" t="n">
-        <v>410.0284350378043</v>
+        <v>409.9348087457767</v>
       </c>
       <c r="K728" t="n">
-        <v>410.8938642891475</v>
+        <v>410.8002379971199</v>
       </c>
       <c r="L728" t="n">
-        <v>411.0451475494303</v>
+        <v>410.9515212574028</v>
       </c>
     </row>
     <row r="729">
@@ -29229,13 +29229,13 @@
         <v>175.4032028184483</v>
       </c>
       <c r="J729" t="n">
-        <v>410.0561032292672</v>
+        <v>409.9611876031502</v>
       </c>
       <c r="K729" t="n">
-        <v>410.9215324806104</v>
+        <v>410.8266168544934</v>
       </c>
       <c r="L729" t="n">
-        <v>411.0728157408932</v>
+        <v>410.9779001147763</v>
       </c>
     </row>
     <row r="730">
@@ -29273,13 +29273,13 @@
         <v>192.7533808857247</v>
       </c>
       <c r="J730" t="n">
-        <v>410.1117484979525</v>
+        <v>410.014239809621</v>
       </c>
       <c r="K730" t="n">
-        <v>410.9771777492957</v>
+        <v>410.8796690609642</v>
       </c>
       <c r="L730" t="n">
-        <v>411.1284610095786</v>
+        <v>411.0309523212471</v>
       </c>
     </row>
     <row r="731">
@@ -29317,13 +29317,13 @@
         <v>197.0750881526188</v>
       </c>
       <c r="J731" t="n">
-        <v>410.1943445183664</v>
+        <v>410.0929868663285</v>
       </c>
       <c r="K731" t="n">
-        <v>411.0597737697096</v>
+        <v>410.9584161176717</v>
       </c>
       <c r="L731" t="n">
-        <v>411.2110570299925</v>
+        <v>411.1096993779546</v>
       </c>
     </row>
     <row r="732">
@@ -39770,22 +39770,22 @@
         <v>6.62</v>
       </c>
       <c r="G1006" t="n">
-        <v>379.173276934123</v>
+        <v>370.473276934123</v>
       </c>
       <c r="H1006" t="n">
-        <v>415.2</v>
+        <v>406.5</v>
       </c>
       <c r="I1006" t="n">
-        <v>453.6545021494341</v>
+        <v>444.9545021494341</v>
       </c>
       <c r="J1006" t="n">
-        <v>270.2837350610071</v>
+        <v>270.2735683943404</v>
       </c>
       <c r="K1006" t="n">
-        <v>270.416</v>
+        <v>270.4058333333333</v>
       </c>
       <c r="L1006" t="n">
-        <v>270.8122122363447</v>
+        <v>270.8020455696781</v>
       </c>
     </row>
     <row r="1007">
@@ -39799,7 +39799,7 @@
       </c>
       <c r="C1007" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2019_2021_2018_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D1007" t="n">
@@ -39814,22 +39814,22 @@
         <v>5.23</v>
       </c>
       <c r="G1007" t="n">
-        <v>322.2495003355559</v>
+        <v>367.598276934123</v>
       </c>
       <c r="H1007" t="n">
-        <v>358.2762234014329</v>
+        <v>403.625</v>
       </c>
       <c r="I1007" t="n">
-        <v>396.730725550867</v>
+        <v>442.0795021494341</v>
       </c>
       <c r="J1007" t="n">
-        <v>270.3996134308133</v>
+        <v>270.2164850610071</v>
       </c>
       <c r="K1007" t="n">
-        <v>270.5318783698062</v>
+        <v>270.34875</v>
       </c>
       <c r="L1007" t="n">
-        <v>270.9280906061509</v>
+        <v>270.7449622363447</v>
       </c>
     </row>
     <row r="1008">
@@ -39843,7 +39843,7 @@
       </c>
       <c r="C1008" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2019_2021_2018_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D1008" t="n">
@@ -39858,22 +39858,22 @@
         <v>6.24</v>
       </c>
       <c r="G1008" t="n">
-        <v>296.2885181473085</v>
+        <v>368.723276934123</v>
       </c>
       <c r="H1008" t="n">
-        <v>332.3152412131856</v>
+        <v>404.75</v>
       </c>
       <c r="I1008" t="n">
-        <v>370.7697433626196</v>
+        <v>443.2045021494341</v>
       </c>
       <c r="J1008" t="n">
-        <v>270.4154149158235</v>
+        <v>270.1281517276738</v>
       </c>
       <c r="K1008" t="n">
-        <v>270.5476798548164</v>
+        <v>270.2604166666667</v>
       </c>
       <c r="L1008" t="n">
-        <v>270.9438920911612</v>
+        <v>270.6566289030114</v>
       </c>
     </row>
     <row r="1009">
@@ -39887,7 +39887,7 @@
       </c>
       <c r="C1009" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2019_2021_2018_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D1009" t="n">
@@ -39902,22 +39902,22 @@
         <v>4.5</v>
       </c>
       <c r="G1009" t="n">
-        <v>269.6682470064975</v>
+        <v>342.1906682384708</v>
       </c>
       <c r="H1009" t="n">
-        <v>305.6949700723745</v>
+        <v>378.2173913043478</v>
       </c>
       <c r="I1009" t="n">
-        <v>344.1494722218086</v>
+        <v>416.6718934537819</v>
       </c>
       <c r="J1009" t="n">
-        <v>270.412780575636</v>
+        <v>270.0416481044854</v>
       </c>
       <c r="K1009" t="n">
-        <v>270.5450455146289</v>
+        <v>270.1739130434783</v>
       </c>
       <c r="L1009" t="n">
-        <v>270.9412577509736</v>
+        <v>270.570125279823</v>
       </c>
     </row>
     <row r="1010">
@@ -39931,7 +39931,7 @@
       </c>
       <c r="C1010" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2019_2021_2018_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D1010" t="n">
@@ -39946,22 +39946,22 @@
         <v>4.17</v>
       </c>
       <c r="G1010" t="n">
-        <v>255.5915605650873</v>
+        <v>357.973276934123</v>
       </c>
       <c r="H1010" t="n">
-        <v>291.6182836309644</v>
+        <v>394</v>
       </c>
       <c r="I1010" t="n">
-        <v>330.0727857803984</v>
+        <v>432.4545021494341</v>
       </c>
       <c r="J1010" t="n">
-        <v>270.4130344829491</v>
+        <v>269.951852708066</v>
       </c>
       <c r="K1010" t="n">
-        <v>270.545299421942</v>
+        <v>270.0841176470589</v>
       </c>
       <c r="L1010" t="n">
-        <v>270.9415116582867</v>
+        <v>270.4803298834036</v>
       </c>
     </row>
     <row r="1011">
@@ -39975,7 +39975,7 @@
       </c>
       <c r="C1011" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2019_2021_2018_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D1011" t="n">
@@ -39990,22 +39990,22 @@
         <v>2.64</v>
       </c>
       <c r="G1011" t="n">
-        <v>241.0781081951391</v>
+        <v>360.8899436007896</v>
       </c>
       <c r="H1011" t="n">
-        <v>277.1048312610161</v>
+        <v>396.9166666666667</v>
       </c>
       <c r="I1011" t="n">
-        <v>315.5593334104502</v>
+        <v>435.3711688161007</v>
       </c>
       <c r="J1011" t="n">
-        <v>270.4343666389942</v>
+        <v>269.9144017276738</v>
       </c>
       <c r="K1011" t="n">
-        <v>270.566631577987</v>
+        <v>270.0466666666667</v>
       </c>
       <c r="L1011" t="n">
-        <v>270.9628438143318</v>
+        <v>270.4428789030114</v>
       </c>
     </row>
     <row r="1012">
@@ -40019,7 +40019,7 @@
       </c>
       <c r="C1012" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2019_2021_2018_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D1012" t="n">
@@ -40034,22 +40034,22 @@
         <v>5</v>
       </c>
       <c r="G1012" t="n">
-        <v>239.7265105060795</v>
+        <v>361.2649436007896</v>
       </c>
       <c r="H1012" t="n">
-        <v>275.7532335719566</v>
+        <v>397.2916666666667</v>
       </c>
       <c r="I1012" t="n">
-        <v>314.2077357213906</v>
+        <v>435.7461688161007</v>
       </c>
       <c r="J1012" t="n">
-        <v>270.415613317329</v>
+        <v>269.8648183943405</v>
       </c>
       <c r="K1012" t="n">
-        <v>270.5478782563218</v>
+        <v>269.9970833333334</v>
       </c>
       <c r="L1012" t="n">
-        <v>270.9440904926666</v>
+        <v>270.3932955696781</v>
       </c>
     </row>
     <row r="1013">
@@ -40063,7 +40063,7 @@
       </c>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2019_2021_2018_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D1013" t="n">
@@ -40078,22 +40078,22 @@
         <v>5.04</v>
       </c>
       <c r="G1013" t="n">
-        <v>238.3749128170201</v>
+        <v>361.0149436007896</v>
       </c>
       <c r="H1013" t="n">
-        <v>274.4016358828971</v>
+        <v>397.0416666666667</v>
       </c>
       <c r="I1013" t="n">
-        <v>312.8561380323312</v>
+        <v>435.4961688161007</v>
       </c>
       <c r="J1013" t="n">
-        <v>270.3694795817081</v>
+        <v>269.7973183943405</v>
       </c>
       <c r="K1013" t="n">
-        <v>270.501744520701</v>
+        <v>269.9295833333334</v>
       </c>
       <c r="L1013" t="n">
-        <v>270.8979567570457</v>
+        <v>270.3257955696781</v>
       </c>
     </row>
     <row r="1014">
@@ -40107,7 +40107,7 @@
       </c>
       <c r="C1014" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2019_2021_2018_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D1014" t="n">
@@ -40122,22 +40122,22 @@
         <v>2.25</v>
       </c>
       <c r="G1014" t="n">
-        <v>225.9900992614616</v>
+        <v>352.098276934123</v>
       </c>
       <c r="H1014" t="n">
-        <v>262.0168223273386</v>
+        <v>388.125</v>
       </c>
       <c r="I1014" t="n">
-        <v>300.4713244767727</v>
+        <v>426.5795021494341</v>
       </c>
       <c r="J1014" t="n">
-        <v>270.3721683430068</v>
+        <v>269.7785683943404</v>
       </c>
       <c r="K1014" t="n">
-        <v>270.5044332819997</v>
+        <v>269.9108333333333</v>
       </c>
       <c r="L1014" t="n">
-        <v>270.9006455183444</v>
+        <v>270.3070455696781</v>
       </c>
     </row>
     <row r="1015">
@@ -40151,7 +40151,7 @@
       </c>
       <c r="C1015" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2019_2021_2018_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D1015" t="n">
@@ -40166,22 +40166,22 @@
         <v>3.85</v>
       </c>
       <c r="G1015" t="n">
-        <v>209.4849533650288</v>
+        <v>410.6816102674563</v>
       </c>
       <c r="H1015" t="n">
-        <v>245.5116764309059</v>
+        <v>446.7083333333333</v>
       </c>
       <c r="I1015" t="n">
-        <v>283.9661785803399</v>
+        <v>485.1628354827674</v>
       </c>
       <c r="J1015" t="n">
-        <v>270.3609086086894</v>
+        <v>269.8739850610071</v>
       </c>
       <c r="K1015" t="n">
-        <v>270.4931735476823</v>
+        <v>270.00625</v>
       </c>
       <c r="L1015" t="n">
-        <v>270.8893857840271</v>
+        <v>270.4024622363447</v>
       </c>
     </row>
     <row r="1016">
@@ -40195,7 +40195,7 @@
       </c>
       <c r="C1016" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2019_2021_2018_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D1016" t="n">
@@ -40210,22 +40210,22 @@
         <v>2.11</v>
       </c>
       <c r="G1016" t="n">
-        <v>231.139259681612</v>
+        <v>398.973276934123</v>
       </c>
       <c r="H1016" t="n">
-        <v>267.165982747489</v>
+        <v>435</v>
       </c>
       <c r="I1016" t="n">
-        <v>305.6204848969231</v>
+        <v>473.4545021494341</v>
       </c>
       <c r="J1016" t="n">
-        <v>270.3423953250727</v>
+        <v>270.0581517276738</v>
       </c>
       <c r="K1016" t="n">
-        <v>270.4746602640656</v>
+        <v>270.1904166666666</v>
       </c>
       <c r="L1016" t="n">
-        <v>270.8708725004104</v>
+        <v>270.5866289030114</v>
       </c>
     </row>
     <row r="1017">
@@ -40239,7 +40239,7 @@
       </c>
       <c r="C1017" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2019_2021_2018_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D1017" t="n">
@@ -40254,22 +40254,22 @@
         <v>5.76</v>
       </c>
       <c r="G1017" t="n">
-        <v>231.167889630713</v>
+        <v>392.7649436007896</v>
       </c>
       <c r="H1017" t="n">
-        <v>267.19461269659</v>
+        <v>428.7916666666667</v>
       </c>
       <c r="I1017" t="n">
-        <v>305.6491148460241</v>
+        <v>467.2461688161007</v>
       </c>
       <c r="J1017" t="n">
-        <v>270.3296694686344</v>
+        <v>270.2002350610071</v>
       </c>
       <c r="K1017" t="n">
-        <v>270.4619344076273</v>
+        <v>270.3325</v>
       </c>
       <c r="L1017" t="n">
-        <v>270.858146643972</v>
+        <v>270.7287122363447</v>
       </c>
     </row>
     <row r="1018">
@@ -40283,7 +40283,7 @@
       </c>
       <c r="C1018" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2019_2021_2018_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D1018" t="n">
@@ -40298,22 +40298,22 @@
         <v>6.54</v>
       </c>
       <c r="G1018" t="n">
-        <v>236.6913452578983</v>
+        <v>386.8899436007896</v>
       </c>
       <c r="H1018" t="n">
-        <v>272.7180683237753</v>
+        <v>422.9166666666667</v>
       </c>
       <c r="I1018" t="n">
-        <v>311.1725704732094</v>
+        <v>461.3711688161007</v>
       </c>
       <c r="J1018" t="n">
-        <v>270.3534069138219</v>
+        <v>270.3114850610071</v>
       </c>
       <c r="K1018" t="n">
-        <v>270.4856718528147</v>
+        <v>270.44375</v>
       </c>
       <c r="L1018" t="n">
-        <v>270.8818840891595</v>
+        <v>270.8399622363448</v>
       </c>
     </row>
     <row r="1019">
@@ -40327,7 +40327,7 @@
       </c>
       <c r="C1019" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2019_2021_2018_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D1019" t="n">
@@ -40342,22 +40342,22 @@
         <v>5.37</v>
       </c>
       <c r="G1019" t="n">
-        <v>229.6473972383586</v>
+        <v>387.0602334558621</v>
       </c>
       <c r="H1019" t="n">
-        <v>265.6741203042357</v>
+        <v>423.0869565217391</v>
       </c>
       <c r="I1019" t="n">
-        <v>304.1286224536697</v>
+        <v>461.5414586711732</v>
       </c>
       <c r="J1019" t="n">
-        <v>270.3929351321966</v>
+        <v>270.2342568001376</v>
       </c>
       <c r="K1019" t="n">
-        <v>270.5252000711894</v>
+        <v>270.3665217391305</v>
       </c>
       <c r="L1019" t="n">
-        <v>270.9214123075342</v>
+        <v>270.7627339754752</v>
       </c>
     </row>
     <row r="1020">
@@ -40371,7 +40371,7 @@
       </c>
       <c r="C1020" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2019_2021_2018_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D1020" t="n">
@@ -40386,22 +40386,22 @@
         <v>5.04</v>
       </c>
       <c r="G1020" t="n">
-        <v>277.682391843298</v>
+        <v>400.2890664078072</v>
       </c>
       <c r="H1020" t="n">
-        <v>313.7091149091751</v>
+        <v>436.3157894736842</v>
       </c>
       <c r="I1020" t="n">
-        <v>352.1636170586091</v>
+        <v>474.7702916231183</v>
       </c>
       <c r="J1020" t="n">
-        <v>270.4596072836734</v>
+        <v>270.2140508504808</v>
       </c>
       <c r="K1020" t="n">
-        <v>270.5918722226663</v>
+        <v>270.3463157894737</v>
       </c>
       <c r="L1020" t="n">
-        <v>270.988084459011</v>
+        <v>270.7425280258184</v>
       </c>
     </row>
     <row r="1021">
@@ -40415,7 +40415,7 @@
       </c>
       <c r="C1021" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2019_2021_2018_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D1021" t="n">
@@ -40430,22 +40430,22 @@
         <v>3.12</v>
       </c>
       <c r="G1021" t="n">
-        <v>292.0813296536218</v>
+        <v>364.473276934123</v>
       </c>
       <c r="H1021" t="n">
-        <v>328.1080527194988</v>
+        <v>400.5</v>
       </c>
       <c r="I1021" t="n">
-        <v>366.5625548689329</v>
+        <v>438.9545021494341</v>
       </c>
       <c r="J1021" t="n">
-        <v>270.5220342686742</v>
+        <v>270.2569017276738</v>
       </c>
       <c r="K1021" t="n">
-        <v>270.6542992076671</v>
+        <v>270.3891666666667</v>
       </c>
       <c r="L1021" t="n">
-        <v>271.0505114440119</v>
+        <v>270.7853789030114</v>
       </c>
     </row>
     <row r="1022">
@@ -40459,7 +40459,7 @@
       </c>
       <c r="C1022" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2019_2021_2018_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D1022" t="n">
@@ -40474,22 +40474,22 @@
         <v>2.83</v>
       </c>
       <c r="G1022" t="n">
-        <v>263.2695418475431</v>
+        <v>329.8066102674563</v>
       </c>
       <c r="H1022" t="n">
-        <v>299.2962649134201</v>
+        <v>365.8333333333333</v>
       </c>
       <c r="I1022" t="n">
-        <v>337.7507670628542</v>
+        <v>404.2878354827674</v>
       </c>
       <c r="J1022" t="n">
-        <v>270.6100469871453</v>
+        <v>270.1006517276738</v>
       </c>
       <c r="K1022" t="n">
-        <v>270.7423119261382</v>
+        <v>270.2329166666667</v>
       </c>
       <c r="L1022" t="n">
-        <v>271.138524162483</v>
+        <v>270.6291289030114</v>
       </c>
     </row>
     <row r="1023">
@@ -40503,7 +40503,7 @@
       </c>
       <c r="C1023" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2019_2021_2018_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D1023" t="n">
@@ -40518,22 +40518,22 @@
         <v>1.38</v>
       </c>
       <c r="G1023" t="n">
-        <v>248.7473739867007</v>
+        <v>332.2649436007896</v>
       </c>
       <c r="H1023" t="n">
-        <v>284.7740970525777</v>
+        <v>368.2916666666667</v>
       </c>
       <c r="I1023" t="n">
-        <v>323.2285992020118</v>
+        <v>406.7461688161007</v>
       </c>
       <c r="J1023" t="n">
-        <v>270.7094577072958</v>
+        <v>269.8781517276738</v>
       </c>
       <c r="K1023" t="n">
-        <v>270.8417226462887</v>
+        <v>270.0104166666667</v>
       </c>
       <c r="L1023" t="n">
-        <v>271.2379348826335</v>
+        <v>270.4066289030114</v>
       </c>
     </row>
     <row r="1024">
@@ -40547,7 +40547,7 @@
       </c>
       <c r="C1024" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2019_2021_2018_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D1024" t="n">
@@ -40562,22 +40562,22 @@
         <v>1.14</v>
       </c>
       <c r="G1024" t="n">
-        <v>257.3157744303468</v>
+        <v>334.3066102674563</v>
       </c>
       <c r="H1024" t="n">
-        <v>293.3424974962239</v>
+        <v>370.3333333333333</v>
       </c>
       <c r="I1024" t="n">
-        <v>331.7969996456579</v>
+        <v>408.7878354827674</v>
       </c>
       <c r="J1024" t="n">
-        <v>270.7967335303838</v>
+        <v>269.6802350610071</v>
       </c>
       <c r="K1024" t="n">
-        <v>270.9289984693767</v>
+        <v>269.8125</v>
       </c>
       <c r="L1024" t="n">
-        <v>271.3252107057215</v>
+        <v>270.2087122363448</v>
       </c>
     </row>
     <row r="1025">
@@ -40591,7 +40591,7 @@
       </c>
       <c r="C1025" t="inlineStr">
         <is>
-          <t>ai_blend_storm_analog_2019_2021_2018_weather_current_boost_enso_scenario</t>
+          <t>observed_anchor</t>
         </is>
       </c>
       <c r="D1025" t="n">
@@ -40606,22 +40606,22 @@
         <v>0.83</v>
       </c>
       <c r="G1025" t="n">
-        <v>264.3597176797218</v>
+        <v>323.6161340769801</v>
       </c>
       <c r="H1025" t="n">
-        <v>300.3864407455988</v>
+        <v>359.6428571428572</v>
       </c>
       <c r="I1025" t="n">
-        <v>338.8409428950329</v>
+        <v>398.0973592922912</v>
       </c>
       <c r="J1025" t="n">
-        <v>270.9039713872641</v>
+        <v>269.5741636324357</v>
       </c>
       <c r="K1025" t="n">
-        <v>271.0362363262569</v>
+        <v>269.7064285714285</v>
       </c>
       <c r="L1025" t="n">
-        <v>271.4324485626017</v>
+        <v>270.1026408077733</v>
       </c>
     </row>
     <row r="1026">
@@ -40650,22 +40650,22 @@
         <v>2.93</v>
       </c>
       <c r="G1026" t="n">
-        <v>246.5600090261201</v>
+        <v>350.5135030864041</v>
       </c>
       <c r="H1026" t="n">
-        <v>282.5867320919971</v>
+        <v>386.5402261522812</v>
       </c>
       <c r="I1026" t="n">
-        <v>321.0412342414312</v>
+        <v>424.9947283017152</v>
       </c>
       <c r="J1026" t="n">
-        <v>271.0369880623599</v>
+        <v>270.708368488678</v>
       </c>
       <c r="K1026" t="n">
-        <v>271.1692530013528</v>
+        <v>270.8406334276709</v>
       </c>
       <c r="L1026" t="n">
-        <v>271.5654652376975</v>
+        <v>271.2368456640157</v>
       </c>
     </row>
     <row r="1027">
@@ -40694,22 +40694,22 @@
         <v>1.84</v>
       </c>
       <c r="G1027" t="n">
-        <v>245.5453496717615</v>
+        <v>315.4842396385085</v>
       </c>
       <c r="H1027" t="n">
-        <v>281.5720727376386</v>
+        <v>351.5109627043855</v>
       </c>
       <c r="I1027" t="n">
-        <v>320.0265748870726</v>
+        <v>389.9654648538196</v>
       </c>
       <c r="J1027" t="n">
-        <v>271.1209751044914</v>
+        <v>270.8009397257387</v>
       </c>
       <c r="K1027" t="n">
-        <v>271.2532400434843</v>
+        <v>270.9332046647315</v>
       </c>
       <c r="L1027" t="n">
-        <v>271.6494522798291</v>
+        <v>271.3294169010763</v>
       </c>
     </row>
     <row r="1028">
@@ -40738,22 +40738,22 @@
         <v>0.34</v>
       </c>
       <c r="G1028" t="n">
-        <v>239.9573028340398</v>
+        <v>275.9416798242025</v>
       </c>
       <c r="H1028" t="n">
-        <v>275.9840258999168</v>
+        <v>311.9684028900796</v>
       </c>
       <c r="I1028" t="n">
-        <v>314.4385280493509</v>
+        <v>350.4229050395136</v>
       </c>
       <c r="J1028" t="n">
-        <v>271.1545149230021</v>
+        <v>270.8418921039256</v>
       </c>
       <c r="K1028" t="n">
-        <v>271.2867798619949</v>
+        <v>270.9741570429185</v>
       </c>
       <c r="L1028" t="n">
-        <v>271.6829920983397</v>
+        <v>271.3703692792632</v>
       </c>
     </row>
     <row r="1029">
@@ -40782,22 +40782,22 @@
         <v>1</v>
       </c>
       <c r="G1029" t="n">
-        <v>234.627546131529</v>
+        <v>238.3787317515873</v>
       </c>
       <c r="H1029" t="n">
-        <v>270.6542691974061</v>
+        <v>274.4054548174644</v>
       </c>
       <c r="I1029" t="n">
-        <v>309.1087713468401</v>
+        <v>312.8599569668984</v>
       </c>
       <c r="J1029" t="n">
-        <v>271.1590541091784</v>
+        <v>270.8462365209588</v>
       </c>
       <c r="K1029" t="n">
-        <v>271.2913190481713</v>
+        <v>270.9785014599517</v>
       </c>
       <c r="L1029" t="n">
-        <v>271.6875312845161</v>
+        <v>271.3747136962965</v>
       </c>
     </row>
     <row r="1030">
@@ -40826,22 +40826,22 @@
         <v>1.77</v>
       </c>
       <c r="G1030" t="n">
-        <v>234.8308349645987</v>
+        <v>236.7249395419063</v>
       </c>
       <c r="H1030" t="n">
-        <v>270.8575580304757</v>
+        <v>272.7516626077834</v>
       </c>
       <c r="I1030" t="n">
-        <v>309.3120601799098</v>
+        <v>311.2061647572174</v>
       </c>
       <c r="J1030" t="n">
-        <v>271.1376738063254</v>
+        <v>270.8245703185933</v>
       </c>
       <c r="K1030" t="n">
-        <v>271.2699387453183</v>
+        <v>270.9568352575861</v>
       </c>
       <c r="L1030" t="n">
-        <v>271.666150981663</v>
+        <v>271.3530474939309</v>
       </c>
     </row>
     <row r="1031">
@@ -40870,22 +40870,22 @@
         <v>2</v>
       </c>
       <c r="G1031" t="n">
-        <v>248.6031380592995</v>
+        <v>248.6390833469108</v>
       </c>
       <c r="H1031" t="n">
-        <v>284.6298611251765</v>
+        <v>284.6658064127878</v>
       </c>
       <c r="I1031" t="n">
-        <v>323.0843632746106</v>
+        <v>323.1203085622219</v>
       </c>
       <c r="J1031" t="n">
-        <v>271.1077609916182</v>
+        <v>270.794257506786</v>
       </c>
       <c r="K1031" t="n">
-        <v>271.2400259306111</v>
+        <v>270.9265224457789</v>
       </c>
       <c r="L1031" t="n">
-        <v>271.6362381669558</v>
+        <v>271.3227346821236</v>
       </c>
     </row>
     <row r="1032">
@@ -40914,22 +40914,22 @@
         <v>0.6</v>
       </c>
       <c r="G1032" t="n">
-        <v>250.1194589938906</v>
+        <v>248.1907147610224</v>
       </c>
       <c r="H1032" t="n">
-        <v>286.1461820597677</v>
+        <v>284.2174378268994</v>
       </c>
       <c r="I1032" t="n">
-        <v>324.6006842092017</v>
+        <v>322.6719399763335</v>
       </c>
       <c r="J1032" t="n">
-        <v>271.109524454052</v>
+        <v>270.7959453018965</v>
       </c>
       <c r="K1032" t="n">
-        <v>271.2417893930449</v>
+        <v>270.9282102408894</v>
       </c>
       <c r="L1032" t="n">
-        <v>271.6380016293896</v>
+        <v>271.3244224772341</v>
       </c>
     </row>
     <row r="1033">
@@ -40958,22 +40958,22 @@
         <v>1.11</v>
       </c>
       <c r="G1033" t="n">
-        <v>244.5152226885452</v>
+        <v>241.293815059907</v>
       </c>
       <c r="H1033" t="n">
-        <v>280.5419457544222</v>
+        <v>277.3205381257841</v>
       </c>
       <c r="I1033" t="n">
-        <v>318.9964479038563</v>
+        <v>315.7750402752181</v>
       </c>
       <c r="J1033" t="n">
-        <v>271.1192663513086</v>
+        <v>270.8052707551196</v>
       </c>
       <c r="K1033" t="n">
-        <v>271.2515312903015</v>
+        <v>270.9375356941125</v>
       </c>
       <c r="L1033" t="n">
-        <v>271.6477435266463</v>
+        <v>271.3337479304572</v>
       </c>
     </row>
     <row r="1034">
@@ -41002,22 +41002,22 @@
         <v>1.86</v>
       </c>
       <c r="G1034" t="n">
-        <v>259.496411857821</v>
+        <v>256.7116340202398</v>
       </c>
       <c r="H1034" t="n">
-        <v>295.523134923698</v>
+        <v>292.7383570861169</v>
       </c>
       <c r="I1034" t="n">
-        <v>333.9776370731321</v>
+        <v>331.1928592355509</v>
       </c>
       <c r="J1034" t="n">
-        <v>271.1415573715572</v>
+        <v>270.8266124296202</v>
       </c>
       <c r="K1034" t="n">
-        <v>271.27382231055</v>
+        <v>270.9588773686131</v>
       </c>
       <c r="L1034" t="n">
-        <v>271.6700345468948</v>
+        <v>271.3550896049578</v>
       </c>
     </row>
     <row r="1035">
@@ -41046,22 +41046,22 @@
         <v>2.81</v>
       </c>
       <c r="G1035" t="n">
-        <v>273.9129518972349</v>
+        <v>271.6115128102297</v>
       </c>
       <c r="H1035" t="n">
-        <v>309.9396749631119</v>
+        <v>307.6382358761067</v>
       </c>
       <c r="I1035" t="n">
-        <v>348.394177112546</v>
+        <v>346.0927380255408</v>
       </c>
       <c r="J1035" t="n">
-        <v>271.1637985846546</v>
+        <v>270.8479099195654</v>
       </c>
       <c r="K1035" t="n">
-        <v>271.2960635236474</v>
+        <v>270.9801748585583</v>
       </c>
       <c r="L1035" t="n">
-        <v>271.6922757599922</v>
+        <v>271.376387094903</v>
       </c>
     </row>
     <row r="1036">
@@ -41093,19 +41093,19 @@
         <v>0</v>
       </c>
       <c r="H1036" t="n">
-        <v>306.9627704271622</v>
+        <v>305.2785444885824</v>
       </c>
       <c r="I1036" t="n">
-        <v>410.4945721712388</v>
+        <v>408.8103462326591</v>
       </c>
       <c r="J1036" t="n">
-        <v>271.0860704987078</v>
+        <v>270.7691562477087</v>
       </c>
       <c r="K1036" t="n">
-        <v>271.3203231456351</v>
+        <v>271.003408894636</v>
       </c>
       <c r="L1036" t="n">
-        <v>271.5836416445611</v>
+        <v>271.266727393562</v>
       </c>
     </row>
     <row r="1037">
@@ -41137,19 +41137,19 @@
         <v>0</v>
       </c>
       <c r="H1037" t="n">
-        <v>355.9796102475017</v>
+        <v>354.6964688263916</v>
       </c>
       <c r="I1037" t="n">
-        <v>459.5114119915784</v>
+        <v>458.2282705704682</v>
       </c>
       <c r="J1037" t="n">
-        <v>271.1278037638469</v>
+        <v>270.8091316606622</v>
       </c>
       <c r="K1037" t="n">
-        <v>271.3620564107742</v>
+        <v>271.0433843075895</v>
       </c>
       <c r="L1037" t="n">
-        <v>271.6253749097002</v>
+        <v>271.3067028065155</v>
       </c>
     </row>
     <row r="1038">
@@ -41181,19 +41181,19 @@
         <v>0</v>
       </c>
       <c r="H1038" t="n">
-        <v>388.8658791736655</v>
+        <v>388.175102831088</v>
       </c>
       <c r="I1038" t="n">
-        <v>492.3976809177422</v>
+        <v>491.7069045751646</v>
       </c>
       <c r="J1038" t="n">
-        <v>271.1550867450372</v>
+        <v>270.835269620003</v>
       </c>
       <c r="K1038" t="n">
-        <v>271.3893393919644</v>
+        <v>271.0695222669303</v>
       </c>
       <c r="L1038" t="n">
-        <v>271.6526578908905</v>
+        <v>271.3328407658563</v>
       </c>
     </row>
     <row r="1039">
@@ -41231,13 +41231,13 @@
         <v>505.2932364483132</v>
       </c>
       <c r="J1039" t="n">
-        <v>271.1943220836064</v>
+        <v>270.8728642509287</v>
       </c>
       <c r="K1039" t="n">
-        <v>271.4285747305337</v>
+        <v>271.1071168978559</v>
       </c>
       <c r="L1039" t="n">
-        <v>271.6918932294597</v>
+        <v>271.3704353967819</v>
       </c>
     </row>
     <row r="1040">
@@ -41269,19 +41269,19 @@
         <v>0</v>
       </c>
       <c r="H1040" t="n">
-        <v>406.5224614782643</v>
+        <v>406.5224614782644</v>
       </c>
       <c r="I1040" t="n">
         <v>510.054263222341</v>
       </c>
       <c r="J1040" t="n">
-        <v>271.2699177403042</v>
+        <v>270.9452987173246</v>
       </c>
       <c r="K1040" t="n">
-        <v>271.5041703872315</v>
+        <v>271.1795513642519</v>
       </c>
       <c r="L1040" t="n">
-        <v>271.7674888861575</v>
+        <v>271.4428698631779</v>
       </c>
     </row>
     <row r="1041">
@@ -41310,22 +41310,22 @@
         <v>1.39</v>
       </c>
       <c r="G1041" t="n">
-        <v>16.37685094018809</v>
+        <v>16.37685094018815</v>
       </c>
       <c r="H1041" t="n">
-        <v>436.9732797066778</v>
+        <v>436.9732797066779</v>
       </c>
       <c r="I1041" t="n">
         <v>540.5050814507545</v>
       </c>
       <c r="J1041" t="n">
-        <v>271.3424208993901</v>
+        <v>271.0147700053566</v>
       </c>
       <c r="K1041" t="n">
-        <v>271.5766735463174</v>
+        <v>271.2490226522838</v>
       </c>
       <c r="L1041" t="n">
-        <v>271.8399920452434</v>
+        <v>271.5123411512099</v>
       </c>
     </row>
     <row r="1042">
@@ -41354,7 +41354,7 @@
         <v>1.11</v>
       </c>
       <c r="G1042" t="n">
-        <v>35.04694242132524</v>
+        <v>35.0469424213253</v>
       </c>
       <c r="H1042" t="n">
         <v>455.643371187815</v>
@@ -41363,13 +41363,13 @@
         <v>559.1751729318917</v>
       </c>
       <c r="J1042" t="n">
-        <v>271.4044780152799</v>
+        <v>271.0742320733102</v>
       </c>
       <c r="K1042" t="n">
-        <v>271.6387306622072</v>
+        <v>271.3084847202374</v>
       </c>
       <c r="L1042" t="n">
-        <v>271.9020491611332</v>
+        <v>271.5718032191634</v>
       </c>
     </row>
     <row r="1043">
@@ -41407,13 +41407,13 @@
         <v>549.0943867684896</v>
       </c>
       <c r="J1043" t="n">
-        <v>271.5010524672222</v>
+        <v>271.1667680628034</v>
       </c>
       <c r="K1043" t="n">
-        <v>271.7353051141494</v>
+        <v>271.4010207097307</v>
       </c>
       <c r="L1043" t="n">
-        <v>271.9986236130754</v>
+        <v>271.6643392086567</v>
       </c>
     </row>
     <row r="1044">
@@ -41442,22 +41442,22 @@
         <v>0.08</v>
       </c>
       <c r="G1044" t="n">
-        <v>4.931470899748888</v>
+        <v>4.931470899749002</v>
       </c>
       <c r="H1044" t="n">
-        <v>425.5278996662386</v>
+        <v>425.5278996662387</v>
       </c>
       <c r="I1044" t="n">
-        <v>529.0597014103153</v>
+        <v>529.0597014103154</v>
       </c>
       <c r="J1044" t="n">
-        <v>271.5837944763206</v>
+        <v>271.246050041946</v>
       </c>
       <c r="K1044" t="n">
-        <v>271.8180471232479</v>
+        <v>271.4803026888733</v>
       </c>
       <c r="L1044" t="n">
-        <v>272.0813656221739</v>
+        <v>271.7436211877993</v>
       </c>
     </row>
     <row r="1045">
@@ -41492,16 +41492,16 @@
         <v>411.7216210510636</v>
       </c>
       <c r="I1045" t="n">
-        <v>515.2534227951402</v>
+        <v>515.2534227951403</v>
       </c>
       <c r="J1045" t="n">
-        <v>271.6202807271526</v>
+        <v>271.2810105439808</v>
       </c>
       <c r="K1045" t="n">
-        <v>271.8545333740798</v>
+        <v>271.5152631909081</v>
       </c>
       <c r="L1045" t="n">
-        <v>272.1178518730059</v>
+        <v>271.7785816898341</v>
       </c>
     </row>
     <row r="1046">
@@ -41539,13 +41539,13 @@
         <v>551.5434766731134</v>
       </c>
       <c r="J1046" t="n">
-        <v>271.6466352571467</v>
+        <v>271.3062630042495</v>
       </c>
       <c r="K1046" t="n">
-        <v>271.880887904074</v>
+        <v>271.5405156511767</v>
       </c>
       <c r="L1046" t="n">
-        <v>272.144206403</v>
+        <v>271.8038341501028</v>
       </c>
     </row>
     <row r="1047">
@@ -41583,13 +41583,13 @@
         <v>550.2530508352065</v>
       </c>
       <c r="J1047" t="n">
-        <v>271.6640444899826</v>
+        <v>271.3229442336469</v>
       </c>
       <c r="K1047" t="n">
-        <v>271.8982971369098</v>
+        <v>271.5571968805741</v>
       </c>
       <c r="L1047" t="n">
-        <v>272.1616156358359</v>
+        <v>271.8205153795001</v>
       </c>
     </row>
     <row r="1048">
@@ -41618,22 +41618,22 @@
         <v>0.09</v>
       </c>
       <c r="G1048" t="n">
-        <v>59.47262401336866</v>
+        <v>59.47262401336877</v>
       </c>
       <c r="H1048" t="n">
-        <v>480.0690527798584</v>
+        <v>480.0690527798585</v>
       </c>
       <c r="I1048" t="n">
-        <v>583.600854523935</v>
+        <v>583.6008545239351</v>
       </c>
       <c r="J1048" t="n">
-        <v>271.6841667464652</v>
+        <v>271.34222503594</v>
       </c>
       <c r="K1048" t="n">
-        <v>271.9184193933925</v>
+        <v>271.5764776828672</v>
       </c>
       <c r="L1048" t="n">
-        <v>272.1817378923185</v>
+        <v>271.8397961817932</v>
       </c>
     </row>
     <row r="1049">
@@ -41671,13 +41671,13 @@
         <v>570.4783818938093</v>
       </c>
       <c r="J1049" t="n">
-        <v>271.7018141647164</v>
+        <v>271.3591344905321</v>
       </c>
       <c r="K1049" t="n">
-        <v>271.9360668116437</v>
+        <v>271.5933871374594</v>
       </c>
       <c r="L1049" t="n">
-        <v>272.1993853105697</v>
+        <v>271.8567056363854</v>
       </c>
     </row>
     <row r="1050">
@@ -41706,22 +41706,22 @@
         <v>0.78</v>
       </c>
       <c r="G1050" t="n">
-        <v>73.85595762432217</v>
+        <v>73.85595762432223</v>
       </c>
       <c r="H1050" t="n">
-        <v>494.4523863908119</v>
+        <v>494.452386390812</v>
       </c>
       <c r="I1050" t="n">
-        <v>597.9841881348885</v>
+        <v>597.9841881348887</v>
       </c>
       <c r="J1050" t="n">
-        <v>271.7160732933696</v>
+        <v>271.3727973439338</v>
       </c>
       <c r="K1050" t="n">
-        <v>271.9503259402968</v>
+        <v>271.6070499908611</v>
       </c>
       <c r="L1050" t="n">
-        <v>272.2136444392228</v>
+        <v>271.8703684897871</v>
       </c>
     </row>
     <row r="1051">
@@ -41750,22 +41750,22 @@
         <v>0.87</v>
       </c>
       <c r="G1051" t="n">
-        <v>69.67711509324391</v>
+        <v>69.67711509324397</v>
       </c>
       <c r="H1051" t="n">
-        <v>490.2735438597336</v>
+        <v>490.2735438597337</v>
       </c>
       <c r="I1051" t="n">
         <v>593.8053456038103</v>
       </c>
       <c r="J1051" t="n">
-        <v>271.7154773253627</v>
+        <v>271.3721932411653</v>
       </c>
       <c r="K1051" t="n">
-        <v>271.94972997229</v>
+        <v>271.6064458880926</v>
       </c>
       <c r="L1051" t="n">
-        <v>272.213048471216</v>
+        <v>271.8697643870186</v>
       </c>
     </row>
     <row r="1052">
@@ -41803,13 +41803,13 @@
         <v>569.3423054498203</v>
       </c>
       <c r="J1052" t="n">
-        <v>271.7120794987172</v>
+        <v>271.3687490353357</v>
       </c>
       <c r="K1052" t="n">
-        <v>271.9463321456445</v>
+        <v>271.6030016822629</v>
       </c>
       <c r="L1052" t="n">
-        <v>272.2096506445705</v>
+        <v>271.8663201811889</v>
       </c>
     </row>
     <row r="1053">
@@ -41838,22 +41838,22 @@
         <v>0.19</v>
       </c>
       <c r="G1053" t="n">
-        <v>18.39844081439389</v>
+        <v>18.39844081439395</v>
       </c>
       <c r="H1053" t="n">
-        <v>438.9948695808836</v>
+        <v>438.9948695808837</v>
       </c>
       <c r="I1053" t="n">
         <v>542.5266713249603</v>
       </c>
       <c r="J1053" t="n">
-        <v>271.7120835037877</v>
+        <v>271.3687528729258</v>
       </c>
       <c r="K1053" t="n">
-        <v>271.946336150715</v>
+        <v>271.603005519853</v>
       </c>
       <c r="L1053" t="n">
-        <v>272.209654649641</v>
+        <v>271.866324018779</v>
       </c>
     </row>
     <row r="1054">
@@ -41891,13 +41891,13 @@
         <v>531.7825045865409</v>
       </c>
       <c r="J1054" t="n">
-        <v>271.7008868559845</v>
+        <v>271.3574033946682</v>
       </c>
       <c r="K1054" t="n">
-        <v>271.9351395029117</v>
+        <v>271.5916560415954</v>
       </c>
       <c r="L1054" t="n">
-        <v>272.1984580018378</v>
+        <v>271.8549745405214</v>
       </c>
     </row>
     <row r="1055">
@@ -41935,13 +41935,13 @@
         <v>522.7933406989454</v>
       </c>
       <c r="J1055" t="n">
-        <v>271.693647797625</v>
+        <v>271.3500655256111</v>
       </c>
       <c r="K1055" t="n">
-        <v>271.9279004445523</v>
+        <v>271.5843181725384</v>
       </c>
       <c r="L1055" t="n">
-        <v>272.1912189434783</v>
+        <v>271.8476366714644</v>
       </c>
     </row>
     <row r="1056">
@@ -41973,19 +41973,19 @@
         <v>0</v>
       </c>
       <c r="H1056" t="n">
-        <v>403.4241787893503</v>
+        <v>403.4241787893504</v>
       </c>
       <c r="I1056" t="n">
         <v>506.955980533427</v>
       </c>
       <c r="J1056" t="n">
-        <v>271.6824227258624</v>
+        <v>271.3386872354166</v>
       </c>
       <c r="K1056" t="n">
-        <v>271.9166753727896</v>
+        <v>271.5729398823439</v>
       </c>
       <c r="L1056" t="n">
-        <v>272.1799938717156</v>
+        <v>271.8362583812699</v>
       </c>
     </row>
     <row r="1057">
@@ -42017,19 +42017,19 @@
         <v>0</v>
       </c>
       <c r="H1057" t="n">
-        <v>375.198558975707</v>
+        <v>375.1985589757071</v>
       </c>
       <c r="I1057" t="n">
-        <v>478.7303607197836</v>
+        <v>478.7303607197837</v>
       </c>
       <c r="J1057" t="n">
-        <v>271.649925506452</v>
+        <v>271.3057464399558</v>
       </c>
       <c r="K1057" t="n">
-        <v>271.8841781533792</v>
+        <v>271.5399990868831</v>
       </c>
       <c r="L1057" t="n">
-        <v>272.1474966523052</v>
+        <v>271.8033175858091</v>
       </c>
     </row>
     <row r="1058">
@@ -42067,13 +42067,13 @@
         <v>450.6454215556127</v>
       </c>
       <c r="J1058" t="n">
-        <v>271.6013649006436</v>
+        <v>271.2565229983073</v>
       </c>
       <c r="K1058" t="n">
-        <v>271.8356175475708</v>
+        <v>271.4907756452345</v>
       </c>
       <c r="L1058" t="n">
-        <v>272.0989360464969</v>
+        <v>271.7540941441605</v>
       </c>
     </row>
     <row r="1059">
@@ -42111,13 +42111,13 @@
         <v>432.9877169343702</v>
       </c>
       <c r="J1059" t="n">
-        <v>271.5570515781421</v>
+        <v>271.2116048139459</v>
       </c>
       <c r="K1059" t="n">
-        <v>271.7913042250693</v>
+        <v>271.4458574608732</v>
       </c>
       <c r="L1059" t="n">
-        <v>272.0546227239954</v>
+        <v>271.7091759597992</v>
       </c>
     </row>
     <row r="1060">
@@ -42155,13 +42155,13 @@
         <v>413.1818726118213</v>
       </c>
       <c r="J1060" t="n">
-        <v>271.4992757637463</v>
+        <v>271.1530403792305</v>
       </c>
       <c r="K1060" t="n">
-        <v>271.7335284106735</v>
+        <v>271.3872930261577</v>
       </c>
       <c r="L1060" t="n">
-        <v>271.9968469095995</v>
+        <v>271.6506115250838</v>
       </c>
     </row>
     <row r="1061">
@@ -42193,19 +42193,19 @@
         <v>0</v>
       </c>
       <c r="H1061" t="n">
-        <v>294.6384530602719</v>
+        <v>294.638453060272</v>
       </c>
       <c r="I1061" t="n">
-        <v>398.1702548043485</v>
+        <v>398.1702548043486</v>
       </c>
       <c r="J1061" t="n">
-        <v>271.4123863728775</v>
+        <v>271.064964977573</v>
       </c>
       <c r="K1061" t="n">
-        <v>271.6466390198048</v>
+        <v>271.2992176245002</v>
       </c>
       <c r="L1061" t="n">
-        <v>271.9099575187308</v>
+        <v>271.5625361234262</v>
       </c>
     </row>
     <row r="1062">
@@ -42237,19 +42237,19 @@
         <v>0</v>
       </c>
       <c r="H1062" t="n">
-        <v>291.5981768706375</v>
+        <v>291.5981768706376</v>
       </c>
       <c r="I1062" t="n">
         <v>395.1299786147142</v>
       </c>
       <c r="J1062" t="n">
-        <v>271.4017400668631</v>
+        <v>271.0541733530833</v>
       </c>
       <c r="K1062" t="n">
-        <v>271.6359927137904</v>
+        <v>271.2884260000106</v>
       </c>
       <c r="L1062" t="n">
-        <v>271.8993112127164</v>
+        <v>271.5517444989366</v>
       </c>
     </row>
     <row r="1063">
@@ -42287,13 +42287,13 @@
         <v>431.5201490468135</v>
       </c>
       <c r="J1063" t="n">
-        <v>271.4038142623363</v>
+        <v>271.0561600913946</v>
       </c>
       <c r="K1063" t="n">
-        <v>271.6380669092635</v>
+        <v>271.2904127383218</v>
       </c>
       <c r="L1063" t="n">
-        <v>271.9013854081895</v>
+        <v>271.5537312372479</v>
       </c>
     </row>
     <row r="1064">
@@ -42325,19 +42325,19 @@
         <v>0</v>
       </c>
       <c r="H1064" t="n">
-        <v>353.3763099770431</v>
+        <v>353.3763099770432</v>
       </c>
       <c r="I1064" t="n">
         <v>456.9081117211198</v>
       </c>
       <c r="J1064" t="n">
-        <v>271.4022022911603</v>
+        <v>271.0545254883958</v>
       </c>
       <c r="K1064" t="n">
-        <v>271.6364549380876</v>
+        <v>271.288778135323</v>
       </c>
       <c r="L1064" t="n">
-        <v>271.8997734370136</v>
+        <v>271.552096634249</v>
       </c>
     </row>
     <row r="1065">
@@ -42369,19 +42369,19 @@
         <v>0</v>
       </c>
       <c r="H1065" t="n">
-        <v>405.68902722063</v>
+        <v>405.6890272206301</v>
       </c>
       <c r="I1065" t="n">
-        <v>509.2208289647066</v>
+        <v>509.2208289647067</v>
       </c>
       <c r="J1065" t="n">
-        <v>271.4074504368367</v>
+        <v>271.0595487521041</v>
       </c>
       <c r="K1065" t="n">
-        <v>271.641703083764</v>
+        <v>271.2938013990313</v>
       </c>
       <c r="L1065" t="n">
-        <v>271.90502158269</v>
+        <v>271.5571198979574</v>
       </c>
     </row>
     <row r="1066">
@@ -42410,22 +42410,22 @@
         <v>0.15</v>
       </c>
       <c r="G1066" t="n">
-        <v>246.7894737681575</v>
+        <v>246.7894737681576</v>
       </c>
       <c r="H1066" t="n">
         <v>292.8039618593652</v>
       </c>
       <c r="I1066" t="n">
-        <v>351.5384274239352</v>
+        <v>351.5384274239353</v>
       </c>
       <c r="J1066" t="n">
-        <v>271.4380711087625</v>
+        <v>271.0888399586382</v>
       </c>
       <c r="K1066" t="n">
-        <v>271.6724862937596</v>
+        <v>271.3232551436353</v>
       </c>
       <c r="L1066" t="n">
-        <v>271.8845155373877</v>
+        <v>271.5352843872634</v>
       </c>
     </row>
     <row r="1067">
@@ -42463,13 +42463,13 @@
         <v>437.4387097798613</v>
       </c>
       <c r="J1067" t="n">
-        <v>271.4224739098624</v>
+        <v>271.0730145820351</v>
       </c>
       <c r="K1067" t="n">
-        <v>271.6568890948595</v>
+        <v>271.3074297670322</v>
       </c>
       <c r="L1067" t="n">
-        <v>271.8689183384877</v>
+        <v>271.5194590106603</v>
       </c>
     </row>
     <row r="1068">
@@ -42498,22 +42498,22 @@
         <v>0.6</v>
       </c>
       <c r="G1068" t="n">
-        <v>366.1274789761802</v>
+        <v>366.1274789761803</v>
       </c>
       <c r="H1068" t="n">
-        <v>412.1419670673879</v>
+        <v>412.141967067388</v>
       </c>
       <c r="I1068" t="n">
-        <v>470.8764326319579</v>
+        <v>470.876432631958</v>
       </c>
       <c r="J1068" t="n">
-        <v>271.3834026816816</v>
+        <v>271.0333640418016</v>
       </c>
       <c r="K1068" t="n">
-        <v>271.6178178666787</v>
+        <v>271.2677792267987</v>
       </c>
       <c r="L1068" t="n">
-        <v>271.8298471103068</v>
+        <v>271.4798084704268</v>
       </c>
     </row>
     <row r="1069">
@@ -42542,7 +42542,7 @@
         <v>0.21</v>
       </c>
       <c r="G1069" t="n">
-        <v>449.8836647470473</v>
+        <v>449.8836647470474</v>
       </c>
       <c r="H1069" t="n">
         <v>495.898152838255</v>
@@ -42551,13 +42551,13 @@
         <v>554.6326184028251</v>
       </c>
       <c r="J1069" t="n">
-        <v>271.3285770336942</v>
+        <v>270.9777146203996</v>
       </c>
       <c r="K1069" t="n">
-        <v>271.5629922186912</v>
+        <v>271.2121298053967</v>
       </c>
       <c r="L1069" t="n">
-        <v>271.7750214623194</v>
+        <v>271.4241590490249</v>
       </c>
     </row>
     <row r="1070">
@@ -42595,13 +42595,13 @@
         <v>569.9397818353196</v>
       </c>
       <c r="J1070" t="n">
-        <v>271.2531874334296</v>
+        <v>270.9011922665658</v>
       </c>
       <c r="K1070" t="n">
-        <v>271.4876026184266</v>
+        <v>271.1356074515629</v>
       </c>
       <c r="L1070" t="n">
-        <v>271.6996318620548</v>
+        <v>271.3476366951911</v>
       </c>
     </row>
     <row r="1071">
@@ -42630,22 +42630,22 @@
         <v>0.03</v>
       </c>
       <c r="G1071" t="n">
-        <v>422.4208028527948</v>
+        <v>422.420802852795</v>
       </c>
       <c r="H1071" t="n">
-        <v>468.4352909440025</v>
+        <v>468.4352909440026</v>
       </c>
       <c r="I1071" t="n">
-        <v>527.1697565085726</v>
+        <v>527.1697565085727</v>
       </c>
       <c r="J1071" t="n">
-        <v>271.1980147587325</v>
+        <v>270.8451906042637</v>
       </c>
       <c r="K1071" t="n">
-        <v>271.4324299437296</v>
+        <v>271.0796057892608</v>
       </c>
       <c r="L1071" t="n">
-        <v>271.6444591873577</v>
+        <v>271.2916350328889</v>
       </c>
     </row>
     <row r="1072">
@@ -42674,22 +42674,22 @@
         <v>0</v>
       </c>
       <c r="G1072" t="n">
-        <v>377.3495232512095</v>
+        <v>377.3495232512096</v>
       </c>
       <c r="H1072" t="n">
-        <v>423.3640113424172</v>
+        <v>423.3640113424173</v>
       </c>
       <c r="I1072" t="n">
-        <v>482.0984769069872</v>
+        <v>482.0984769069873</v>
       </c>
       <c r="J1072" t="n">
-        <v>271.1547476596657</v>
+        <v>270.8012734027859</v>
       </c>
       <c r="K1072" t="n">
-        <v>271.3891628446628</v>
+        <v>271.035688587783</v>
       </c>
       <c r="L1072" t="n">
-        <v>271.6011920882909</v>
+        <v>271.2477178314111</v>
       </c>
     </row>
     <row r="1073">
@@ -42718,22 +42718,22 @@
         <v>0</v>
       </c>
       <c r="G1073" t="n">
-        <v>376.0777977150868</v>
+        <v>376.0777977150869</v>
       </c>
       <c r="H1073" t="n">
-        <v>422.0922858062945</v>
+        <v>422.0922858062946</v>
       </c>
       <c r="I1073" t="n">
-        <v>480.8267513708645</v>
+        <v>480.8267513708646</v>
       </c>
       <c r="J1073" t="n">
-        <v>271.1508906458825</v>
+        <v>270.7973584361005</v>
       </c>
       <c r="K1073" t="n">
-        <v>271.3853058308796</v>
+        <v>271.0317736210976</v>
       </c>
       <c r="L1073" t="n">
-        <v>271.5973350745077</v>
+        <v>271.2438028647258</v>
       </c>
     </row>
     <row r="1074">
@@ -42762,22 +42762,22 @@
         <v>0</v>
       </c>
       <c r="G1074" t="n">
-        <v>367.166335605267</v>
+        <v>367.1663356052671</v>
       </c>
       <c r="H1074" t="n">
-        <v>413.1808236964747</v>
+        <v>413.1808236964748</v>
       </c>
       <c r="I1074" t="n">
-        <v>471.9152892610447</v>
+        <v>471.9152892610448</v>
       </c>
       <c r="J1074" t="n">
-        <v>271.1951261261472</v>
+        <v>270.839639367444</v>
       </c>
       <c r="K1074" t="n">
-        <v>271.4295413111443</v>
+        <v>271.0740545524411</v>
       </c>
       <c r="L1074" t="n">
-        <v>271.6415705547724</v>
+        <v>271.2860837960692</v>
       </c>
     </row>
     <row r="1075">
@@ -42809,19 +42809,19 @@
         <v>338.9889928596587</v>
       </c>
       <c r="H1075" t="n">
-        <v>385.0034809508663</v>
+        <v>385.0034809508664</v>
       </c>
       <c r="I1075" t="n">
         <v>443.7379465154364</v>
       </c>
       <c r="J1075" t="n">
-        <v>271.2991679919302</v>
+        <v>270.939084133448</v>
       </c>
       <c r="K1075" t="n">
-        <v>271.5335831769273</v>
+        <v>271.1734993184451</v>
       </c>
       <c r="L1075" t="n">
-        <v>271.7456124205554</v>
+        <v>271.3855285620733</v>
       </c>
     </row>
     <row r="1076">
@@ -42850,22 +42850,22 @@
         <v>0</v>
       </c>
       <c r="G1076" t="n">
-        <v>333.9619514889401</v>
+        <v>333.9619514889403</v>
       </c>
       <c r="H1076" t="n">
-        <v>379.9764395801478</v>
+        <v>379.9764395801479</v>
       </c>
       <c r="I1076" t="n">
-        <v>438.7109051447179</v>
+        <v>438.710905144718</v>
       </c>
       <c r="J1076" t="n">
-        <v>271.3908649875423</v>
+        <v>271.0267294885492</v>
       </c>
       <c r="K1076" t="n">
-        <v>271.6252801725394</v>
+        <v>271.2611446735463</v>
       </c>
       <c r="L1076" t="n">
-        <v>271.8373094161676</v>
+        <v>271.4731739171744</v>
       </c>
     </row>
     <row r="1077">
@@ -42894,22 +42894,22 @@
         <v>0.04</v>
       </c>
       <c r="G1077" t="n">
-        <v>348.4250357572045</v>
+        <v>348.4250357572046</v>
       </c>
       <c r="H1077" t="n">
-        <v>394.4395238484121</v>
+        <v>394.4395238484123</v>
       </c>
       <c r="I1077" t="n">
-        <v>453.1739894129822</v>
+        <v>453.1739894129823</v>
       </c>
       <c r="J1077" t="n">
-        <v>271.4603598317796</v>
+        <v>271.0931536964549</v>
       </c>
       <c r="K1077" t="n">
-        <v>271.6947750167766</v>
+        <v>271.327568881452</v>
       </c>
       <c r="L1077" t="n">
-        <v>271.9068042604048</v>
+        <v>271.5395981250801</v>
       </c>
     </row>
     <row r="1078">
@@ -42944,16 +42944,16 @@
         <v>361.2434836300063</v>
       </c>
       <c r="I1078" t="n">
-        <v>419.9779491945763</v>
+        <v>419.9779491945764</v>
       </c>
       <c r="J1078" t="n">
-        <v>271.5084191459027</v>
+        <v>271.1390895051924</v>
       </c>
       <c r="K1078" t="n">
-        <v>271.7428343308998</v>
+        <v>271.3735046901895</v>
       </c>
       <c r="L1078" t="n">
-        <v>271.9548635745279</v>
+        <v>271.5855339338177</v>
       </c>
     </row>
     <row r="1079">
@@ -42982,22 +42982,22 @@
         <v>0.11</v>
       </c>
       <c r="G1079" t="n">
-        <v>282.5600812635459</v>
+        <v>282.560081263546</v>
       </c>
       <c r="H1079" t="n">
         <v>328.5745693547536</v>
       </c>
       <c r="I1079" t="n">
-        <v>387.3090349193236</v>
+        <v>387.3090349193237</v>
       </c>
       <c r="J1079" t="n">
-        <v>271.5260649933879</v>
+        <v>271.1559556692208</v>
       </c>
       <c r="K1079" t="n">
-        <v>271.760480178385</v>
+        <v>271.3903708542178</v>
       </c>
       <c r="L1079" t="n">
-        <v>271.9725094220131</v>
+        <v>271.602400097846</v>
       </c>
     </row>
     <row r="1080">
@@ -43026,22 +43026,22 @@
         <v>0</v>
       </c>
       <c r="G1080" t="n">
-        <v>254.7922086679479</v>
+        <v>254.792208667948</v>
       </c>
       <c r="H1080" t="n">
-        <v>300.8066967591556</v>
+        <v>300.8066967591557</v>
       </c>
       <c r="I1080" t="n">
-        <v>359.5411623237256</v>
+        <v>359.5411623237257</v>
       </c>
       <c r="J1080" t="n">
-        <v>271.4926653580733</v>
+        <v>271.1220541933874</v>
       </c>
       <c r="K1080" t="n">
-        <v>271.7270805430704</v>
+        <v>271.3564693783845</v>
       </c>
       <c r="L1080" t="n">
-        <v>271.9391097866986</v>
+        <v>271.5684986220127</v>
       </c>
     </row>
     <row r="1081">
@@ -43070,22 +43070,22 @@
         <v>0.01</v>
       </c>
       <c r="G1081" t="n">
-        <v>249.6805732146489</v>
+        <v>249.680573214649</v>
       </c>
       <c r="H1081" t="n">
-        <v>295.6950613058566</v>
+        <v>295.6950613058567</v>
       </c>
       <c r="I1081" t="n">
-        <v>354.4295268704266</v>
+        <v>354.4295268704267</v>
       </c>
       <c r="J1081" t="n">
-        <v>271.4493717202946</v>
+        <v>271.0781100544449</v>
       </c>
       <c r="K1081" t="n">
-        <v>271.6837869052917</v>
+        <v>271.312525239442</v>
       </c>
       <c r="L1081" t="n">
-        <v>271.8958161489198</v>
+        <v>271.5245544830701</v>
       </c>
     </row>
     <row r="1082">
@@ -43117,19 +43117,19 @@
         <v>239.9577356884702</v>
       </c>
       <c r="H1082" t="n">
-        <v>285.9722237796778</v>
+        <v>285.9722237796779</v>
       </c>
       <c r="I1082" t="n">
         <v>344.7066893442479</v>
       </c>
       <c r="J1082" t="n">
-        <v>271.3918832926141</v>
+        <v>271.019757844208</v>
       </c>
       <c r="K1082" t="n">
-        <v>271.6262984776112</v>
+        <v>271.254173029205</v>
       </c>
       <c r="L1082" t="n">
-        <v>271.8383277212393</v>
+        <v>271.4662022728332</v>
       </c>
     </row>
     <row r="1083">
@@ -43158,22 +43158,22 @@
         <v>0.02</v>
       </c>
       <c r="G1083" t="n">
-        <v>230.7832045737512</v>
+        <v>230.7832045737513</v>
       </c>
       <c r="H1083" t="n">
-        <v>276.7976926649589</v>
+        <v>276.797692664959</v>
       </c>
       <c r="I1083" t="n">
-        <v>335.5321582295289</v>
+        <v>335.532158229529</v>
       </c>
       <c r="J1083" t="n">
-        <v>271.3157244439257</v>
+        <v>270.9424546837396</v>
       </c>
       <c r="K1083" t="n">
-        <v>271.5501396289228</v>
+        <v>271.1768698687367</v>
       </c>
       <c r="L1083" t="n">
-        <v>271.7621688725509</v>
+        <v>271.3888991123649</v>
       </c>
     </row>
     <row r="1084">
@@ -43205,19 +43205,19 @@
         <v>222.5997533670474</v>
       </c>
       <c r="H1084" t="n">
-        <v>268.614241458255</v>
+        <v>268.6142414582551</v>
       </c>
       <c r="I1084" t="n">
         <v>327.3487070228251</v>
       </c>
       <c r="J1084" t="n">
-        <v>271.1987696577266</v>
+        <v>270.8237426133657</v>
       </c>
       <c r="K1084" t="n">
-        <v>271.4331848427237</v>
+        <v>271.0581577983628</v>
       </c>
       <c r="L1084" t="n">
-        <v>271.6452140863518</v>
+        <v>271.2701870419909</v>
       </c>
     </row>
     <row r="1085">
@@ -43246,22 +43246,22 @@
         <v>0</v>
       </c>
       <c r="G1085" t="n">
-        <v>225.0042026083124</v>
+        <v>225.0042026083125</v>
       </c>
       <c r="H1085" t="n">
-        <v>271.0186906995201</v>
+        <v>271.0186906995202</v>
       </c>
       <c r="I1085" t="n">
-        <v>329.7531562640901</v>
+        <v>329.7531562640902</v>
       </c>
       <c r="J1085" t="n">
-        <v>271.0505419296855</v>
+        <v>270.6732877149008</v>
       </c>
       <c r="K1085" t="n">
-        <v>271.2849571146826</v>
+        <v>270.9077028998979</v>
       </c>
       <c r="L1085" t="n">
-        <v>271.4969863583107</v>
+        <v>271.1197321435261</v>
       </c>
     </row>
     <row r="1086">
@@ -43290,22 +43290,22 @@
         <v>0.01</v>
       </c>
       <c r="G1086" t="n">
-        <v>243.4742008306716</v>
+        <v>243.4742008306717</v>
       </c>
       <c r="H1086" t="n">
-        <v>289.4886889218793</v>
+        <v>289.4886889218794</v>
       </c>
       <c r="I1086" t="n">
-        <v>348.2231544864493</v>
+        <v>348.2231544864495</v>
       </c>
       <c r="J1086" t="n">
-        <v>270.920533340691</v>
+        <v>270.5413257040461</v>
       </c>
       <c r="K1086" t="n">
-        <v>271.1549485256881</v>
+        <v>270.7757408890432</v>
       </c>
       <c r="L1086" t="n">
-        <v>271.3669777693162</v>
+        <v>270.9877701326713</v>
       </c>
     </row>
     <row r="1087">
@@ -43334,22 +43334,22 @@
         <v>0.01</v>
       </c>
       <c r="G1087" t="n">
-        <v>244.1060231190522</v>
+        <v>244.1060231190523</v>
       </c>
       <c r="H1087" t="n">
-        <v>290.1205112102599</v>
+        <v>290.12051121026</v>
       </c>
       <c r="I1087" t="n">
-        <v>348.8549767748299</v>
+        <v>348.85497677483</v>
       </c>
       <c r="J1087" t="n">
-        <v>270.8225324571354</v>
+        <v>270.4418523249442</v>
       </c>
       <c r="K1087" t="n">
-        <v>271.0569476421325</v>
+        <v>270.6762675099413</v>
       </c>
       <c r="L1087" t="n">
-        <v>271.2689768857606</v>
+        <v>270.8882967535694</v>
       </c>
     </row>
     <row r="1088">
@@ -43387,13 +43387,13 @@
         <v>332.9903287461394</v>
       </c>
       <c r="J1088" t="n">
-        <v>270.7413329944716</v>
+        <v>270.3594328136157</v>
       </c>
       <c r="K1088" t="n">
-        <v>270.9757481794687</v>
+        <v>270.5938479986128</v>
       </c>
       <c r="L1088" t="n">
-        <v>271.1877774230969</v>
+        <v>270.8058772422409</v>
       </c>
     </row>
     <row r="1089">
@@ -43431,13 +43431,13 @@
         <v>342.3473514044684</v>
       </c>
       <c r="J1089" t="n">
-        <v>270.7025660477295</v>
+        <v>270.3200833807333</v>
       </c>
       <c r="K1089" t="n">
-        <v>270.9369812327266</v>
+        <v>270.5544985657303</v>
       </c>
       <c r="L1089" t="n">
-        <v>271.1490104763548</v>
+        <v>270.7665278093585</v>
       </c>
     </row>
     <row r="1090">
@@ -43466,22 +43466,22 @@
         <v>0</v>
       </c>
       <c r="G1090" t="n">
-        <v>215.3528176089247</v>
+        <v>215.3528176089248</v>
       </c>
       <c r="H1090" t="n">
-        <v>261.3673057001324</v>
+        <v>261.3673057001325</v>
       </c>
       <c r="I1090" t="n">
-        <v>320.1017712647024</v>
+        <v>320.1017712647025</v>
       </c>
       <c r="J1090" t="n">
-        <v>270.7302965112428</v>
+        <v>270.3465885710671</v>
       </c>
       <c r="K1090" t="n">
-        <v>270.9647116962399</v>
+        <v>270.5810037560642</v>
       </c>
       <c r="L1090" t="n">
-        <v>271.1767409398681</v>
+        <v>270.7930329996923</v>
       </c>
     </row>
     <row r="1091">
@@ -43516,16 +43516,16 @@
         <v>265.3865076181294</v>
       </c>
       <c r="I1091" t="n">
-        <v>324.1209731826994</v>
+        <v>324.1209731826995</v>
       </c>
       <c r="J1091" t="n">
-        <v>270.7895124596077</v>
+        <v>270.4031880570965</v>
       </c>
       <c r="K1091" t="n">
-        <v>271.0239276446048</v>
+        <v>270.6376032420936</v>
       </c>
       <c r="L1091" t="n">
-        <v>271.2359568882329</v>
+        <v>270.8496324857218</v>
       </c>
     </row>
     <row r="1092">
@@ -43557,19 +43557,19 @@
         <v>218.0860009048141</v>
       </c>
       <c r="H1092" t="n">
-        <v>264.1004889960217</v>
+        <v>264.1004889960218</v>
       </c>
       <c r="I1092" t="n">
         <v>322.8349545605918</v>
       </c>
       <c r="J1092" t="n">
-        <v>270.8406568341209</v>
+        <v>270.4520726125361</v>
       </c>
       <c r="K1092" t="n">
-        <v>271.075072019118</v>
+        <v>270.6864877975332</v>
       </c>
       <c r="L1092" t="n">
-        <v>271.2871012627461</v>
+        <v>270.8985170411614</v>
       </c>
     </row>
     <row r="1093">
@@ -43598,22 +43598,22 @@
         <v>0</v>
       </c>
       <c r="G1093" t="n">
-        <v>214.9714176172184</v>
+        <v>214.9714176172185</v>
       </c>
       <c r="H1093" t="n">
-        <v>260.9859057084261</v>
+        <v>260.9859057084262</v>
       </c>
       <c r="I1093" t="n">
-        <v>319.7203712729961</v>
+        <v>319.7203712729962</v>
       </c>
       <c r="J1093" t="n">
-        <v>270.8897977890958</v>
+        <v>270.4990422697209</v>
       </c>
       <c r="K1093" t="n">
-        <v>271.1242129740929</v>
+        <v>270.733457454718</v>
       </c>
       <c r="L1093" t="n">
-        <v>271.3362422177211</v>
+        <v>270.9454866983461</v>
       </c>
     </row>
     <row r="1094">
@@ -43648,16 +43648,16 @@
         <v>246.6530681478854</v>
       </c>
       <c r="I1094" t="n">
-        <v>305.3875337124554</v>
+        <v>305.3875337124555</v>
       </c>
       <c r="J1094" t="n">
-        <v>270.9377658784788</v>
+        <v>270.5448908844921</v>
       </c>
       <c r="K1094" t="n">
-        <v>271.1721810634759</v>
+        <v>270.7793060694892</v>
       </c>
       <c r="L1094" t="n">
-        <v>271.3842103071041</v>
+        <v>270.9913353131173</v>
       </c>
     </row>
     <row r="1095">
@@ -43692,16 +43692,16 @@
         <v>258.8580029931799</v>
       </c>
       <c r="I1095" t="n">
-        <v>317.5924685577499</v>
+        <v>317.59246855775</v>
       </c>
       <c r="J1095" t="n">
-        <v>270.9652151500852</v>
+        <v>270.5711273074102</v>
       </c>
       <c r="K1095" t="n">
-        <v>271.1996303350823</v>
+        <v>270.8055424924073</v>
       </c>
       <c r="L1095" t="n">
-        <v>271.4116595787104</v>
+        <v>271.0175717360354</v>
       </c>
     </row>
     <row r="1096">
@@ -43730,22 +43730,22 @@
         <v>0</v>
       </c>
       <c r="G1096" t="n">
-        <v>212.4652714012551</v>
+        <v>212.4652714012552</v>
       </c>
       <c r="H1096" t="n">
         <v>258.4797594924628</v>
       </c>
       <c r="I1096" t="n">
-        <v>317.2142250570328</v>
+        <v>317.2142250570329</v>
       </c>
       <c r="J1096" t="n">
-        <v>270.952023096572</v>
+        <v>270.5577370389489</v>
       </c>
       <c r="K1096" t="n">
-        <v>271.1864382815691</v>
+        <v>270.792152223946</v>
       </c>
       <c r="L1096" t="n">
-        <v>271.3984675251972</v>
+        <v>271.0041814675741</v>
       </c>
     </row>
   </sheetData>
